--- a/docs/projets/batiment-industriel-30x10/Batiment_30x10_Metre_DS_DQE.xlsx
+++ b/docs/projets/batiment-industriel-30x10/Batiment_30x10_Metre_DS_DQE.xlsx
@@ -207,7 +207,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="#,##0.000;(#,##0.000);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -251,6 +251,11 @@
       <name val="Arial"/>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="7">
@@ -356,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -408,6 +413,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,6 +488,66 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="904875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,323 +839,420 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="95" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Notice du classeur - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Notice du classeur - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Objet</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Métré, déboursé sec et devis quantitatif et estimatif (DQE) d'un bâtiment industriel 30 x 10 m, murs en agglos 15 pleins, piliers IPE 220 tous les 5 m encadrés de 2 poteaux BA, contreventements en cornières 50x50x5, entrée 6 m, toiture 2 versants à 20 %, dallage BA 20 cm double nappe HA10, semelles isolées 80 x 80 x 30 en HA12 avec tiges d'ancrage.</t>
-        </is>
-      </c>
+          <t>ENTREPRISE</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Auteur</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Raison sociale</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Moulo Jean Claude - Technicien Génie Civil BTP - Abidjan</t>
+          <t>ASSEYA SILVER CONSTRUCTION (ASC) - Construction métallique et bâtiment</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Date</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Siège</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04/10/2026 - prix du marché d'Abidjan à confirmer par cotations fournisseurs</t>
+          <t>Bouaké</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Téléphone</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>07 08 39 02 66 / 05 05 10 76 82</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>COMMENT MODIFIER</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>asseyasilver@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Cellules bleues sur fond jaune</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N° CC / RCCM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Données modifiables : dimensions, épaisseurs, prix unitaires, rendements, coefficients. Tout le reste se recalcule automatiquement.</t>
+          <t>2245191 D / CI-BKE-01-2022-B13-00153</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Texte noir</t>
+          <t>Banque</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Formules - ne pas écraser.</t>
+          <t>Bank of Africa - compte n° 004619070000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Sol de bonne portance</t>
+          <t>Régime fiscal</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Feuille « Paramètres » : mettre p_EPLAT = 0,20 (une seule couche de latérite) au lieu de 0,40.</t>
+          <t>TEE - Bouaké 1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Changer un prix</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Feuille « Prix » colonne D : la modification se répercute sur tous les sous-détails, le DS et le DQE.</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Changer un rendement</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Objet</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Feuille « Sous-détails » colonne F (quantité par unité d'ouvrage).</t>
+          <t>Métré, déboursé sec et devis quantitatif et estimatif (DQE) d'un bâtiment industriel 30 x 10 m, murs en agglos 15 pleins, piliers IPE 220 tous les 5 m encadrés de 2 poteaux BA, contreventements en cornières 50x50x5, entrée 6 m, toiture 2 versants à 20 %, dallage BA 20 cm double nappe HA10, semelles isolées 80 x 80 x 30 en HA12 avec tiges d'ancrage.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Auteur</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Moulo Jean Claude - Technicien Génie Civil BTP - Abidjan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>FEUILLES</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>04/10/2026 - prix du marché d'Abidjan à confirmer par cotations fournisseurs</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Paramètres</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Dimensions, hypothèses, coefficients K et TVA, grandeurs calculées (noms p_...).</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Prix</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Prix de base : matériaux, main-d'œuvre (h.j), matériel (noms px_...).</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT MODIFIER</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Aciers</t>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Cellules bleues sur fond jaune</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Nomenclature des aciers HA6 / HA10 / HA12 par lot, nombre de barres de 12 m.</t>
+          <t>Données modifiables : dimensions, épaisseurs, prix unitaires, rendements, coefficients. Tout le reste se recalcule automatiquement.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Métré</t>
+          <t>Texte noir</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Avant-métré : formule de chaque quantité (noms q_...).</t>
+          <t>Formules - ne pas écraser.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Sous-détails</t>
+          <t>Sol de bonne portance</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Décomposition matériaux / main-d'œuvre / matériel de chaque prix unitaire.</t>
+          <t>Feuille « Paramètres » : mettre p_EPLAT = 0,20 (une seule couche de latérite) au lieu de 0,40.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Déboursé sec</t>
+          <t>Changer un prix</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Déboursé sec par article et par lot, répartition par nature.</t>
+          <t>Feuille « Prix » colonne D : la modification se répercute sur tous les sous-détails, le DS et le DQE.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>DQE</t>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Changer un rendement</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Devis quantitatif et estimatif : PU = DS x K arrondi à 5 FCFA, récapitulatif HT / TVA 18 % / TTC.</t>
+          <t>Feuille « Sous-détails » colonne F (quantité par unité d'ouvrage).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Matériaux et MO</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Liste de commande des matériaux et besoins en main-d'œuvre et matériel.</t>
-        </is>
-      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>FEUILLES</t>
+        </is>
+      </c>
       <c r="C24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>HYPOTHÈSES CLÉS</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Paramètres</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Dimensions, hypothèses, coefficients K et TVA, grandeurs calculées (noms p_...).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Piliers</t>
+          <t>Prix</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>17 piliers en IPE 220 (S235) de ±0,00 à +6,00 sur platine 15 mm et 4 tiges d'ancrage M20 ; 2 poteaux BA 15x15 (4 HA10, cadres HA6 e = 15) de part et d'autre de chaque IPE.</t>
+          <t>Prix de base : matériaux, main-d'œuvre (h.j), matériel (noms px_...).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Contreventements</t>
+          <t>Aciers</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Cornières 50x50x5 : 4 palées verticales en croix (travées d'extrémité des long pans) et poutre au vent dans 2 travées de toiture.</t>
+          <t>Nomenclature des aciers HA6 / HA10 / HA12 par lot, nombre de barres de 12 m.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Semelles isolées</t>
+          <t>Métré</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>80 x 80 x 30 cm, fond de fouille à -1,20 m, nappe HA12 e = 15 cm dans les 2 sens, fût BA 40 x 40 (4 HA12) jusqu'à ±0,00 recevant les 4 tiges d'ancrage M20 de la platine de l'IPE.</t>
+          <t>Avant-métré : formule de chaque quantité (noms q_...).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Dallage</t>
+          <t>Sous-détails</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20 cm, béton dosé à 350 kg/m³, double nappe HA10 e = 20 cm, chaises HA10, polyane, joints sciés maille 5 m.</t>
+          <t>Décomposition matériaux / main-d'œuvre / matériel de chaque prix unitaire.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>Déboursé sec</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Déboursé sec par article et par lot, répartition par nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>DQE</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Devis quantitatif et estimatif : PU = DS x K arrondi à 5 FCFA, récapitulatif HT / TVA 18 % / TTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Matériaux et MO</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Liste de commande des matériaux et besoins en main-d'œuvre et matériel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>HYPOTHÈSES CLÉS</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Piliers</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>17 piliers en IPE 220 (S235) de ±0,00 à +6,00 sur platine 15 mm et 4 tiges d'ancrage M20 ; 2 poteaux BA 15x15 (4 HA10, cadres HA6 e = 15) de part et d'autre de chaque IPE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Contreventements</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Cornières 50x50x5 : 4 palées verticales en croix (travées d'extrémité des long pans) et poutre au vent dans 2 travées de toiture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Semelles isolées</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>80 x 80 x 30 cm, fond de fouille à -1,20 m, nappe HA12 e = 15 cm dans les 2 sens, fût BA 40 x 40 (4 HA12) jusqu'à ±0,00 recevant les 4 tiges d'ancrage M20 de la platine de l'IPE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Dallage</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>20 cm, béton dosé à 350 kg/m³, double nappe HA10 e = 20 cm, chaises HA10, polyane, joints sciés maille 5 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
           <t>Forme</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Purge et rechargement en latérite par couches de 20 cm compactées à 95 % OPM : 40 cm si mauvaise portance (valeur par défaut), 20 cm sinon.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="5" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Lots 6 à 8 (enduits, fermes + pannes Z 120x2 + tôles bacs 5 ondes, portail) chiffrés séparément.</t>
         </is>
@@ -1099,13 +1262,14 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RNotice du classeur</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RNotice du classeur</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1128,14 +1292,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Paramètres et hypothèses - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Paramètres et hypothèses - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -3080,8 +3244,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RParamètres et hypothèses</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RParamètres et hypothèses</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3109,14 +3273,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prix de base - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Prix de base - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -4391,8 +4555,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RPrix de base</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RPrix de base</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4422,14 +4586,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Nomenclature des aciers - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Nomenclature des aciers - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -5292,8 +5456,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RNomenclature des aciers</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RNomenclature des aciers</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5322,14 +5486,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Avant-métré - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Avant-métré - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -6876,8 +7040,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RAvant-métré</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RAvant-métré</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6911,14 +7075,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sous-détails de prix (déboursé sec unitaire) - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Sous-détails de prix (déboursé sec unitaire) - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -21685,8 +21849,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RSous-détails de prix (déboursé sec unitaire)</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RSous-détails de prix (déboursé sec unitaire)</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -21722,14 +21886,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Déboursé sec - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Déboursé sec - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -25108,8 +25272,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RDéboursé sec</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RDéboursé sec</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -25124,7 +25288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -25139,14 +25303,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Devis quantitatif et estimatif - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Devis quantitatif et estimatif - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -27343,7 +27507,21 @@
     <row r="102">
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Fait à Abidjan, le 04/10/2026 - Moulo Jean Claude, Technicien Génie Civil BTP</t>
+          <t>Fait à Abidjan, le 04/10/2026 - Établi par Moulo Jean Claude, Technicien Génie Civil BTP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Pour ASSEYA SILVER CONSTRUCTION : cachet et signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="41" t="inlineStr">
+        <is>
+          <t>ASSEYA SILVER CONSTRUCTION - N° CC : 2245191 D - RCCM : CI-BKE-01-2022-B13-00153 - Bank of Africa - compte n° 004619070000 - Impôts : TEE - Bouaké 1</t>
         </is>
       </c>
     </row>
@@ -27351,13 +27529,14 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RDevis quantitatif et estimatif</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RDevis quantitatif et estimatif</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -27384,14 +27563,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOULO JEAN CLAUDE - Technicien Génie Civil BTP - Abidjan, Côte d'Ivoire</t>
+          <t>ASSEYA SILVER CONSTRUCTION - Construction métallique et bâtiment - Bouaké - Tél : 07 08 39 02 66 / 05 05 10 76 82 - Email : asseyasilver@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Besoins en matériaux, main-d'œuvre et matériel - Construction d'un bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - BAEL 91 mod. 99 / EC2</t>
+          <t>Besoins en matériaux, main-d'œuvre et matériel - Bâtiment industriel 30,00 x 10,00 m - 04/10/2026 - établi par Moulo Jean Claude, Technicien Génie Civil BTP - BAEL 91 mod. 99 / EC2</t>
         </is>
       </c>
     </row>
@@ -29351,8 +29530,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LMoulo Jean Claude - Technicien Génie Civil BTP&amp;RBesoins en matériaux, main-d'œuvre et matériel</oddHeader>
-    <oddFooter>&amp;CPage &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;LASSEYA SILVER CONSTRUCTION - établi par Moulo Jean Claude&amp;RBesoins en matériaux, main-d'œuvre et matériel</oddHeader>
+    <oddFooter>&amp;LASSEYA SILVER CONSTRUCTION - N° CC 2245191 D - RCCM CI-BKE-01-2022-B13-00153&amp;RPage &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/docs/projets/batiment-industriel-30x10/Batiment_30x10_Metre_DS_DQE.xlsx
+++ b/docs/projets/batiment-industriel-30x10/Batiment_30x10_Metre_DS_DQE.xlsx
@@ -36,11 +36,11 @@
     <definedName name="p_HCH">'Paramètres'!$C$21</definedName>
     <definedName name="p_ZCHI">'Paramètres'!$C$22</definedName>
     <definedName name="p_LINH">'Paramètres'!$C$23</definedName>
-    <definedName name="p_FRL">'Paramètres'!$C$25</definedName>
-    <definedName name="p_FRH">'Paramètres'!$C$26</definedName>
-    <definedName name="p_PROP">'Paramètres'!$C$27</definedName>
-    <definedName name="p_SFB">'Paramètres'!$C$28</definedName>
-    <definedName name="p_SFH">'Paramètres'!$C$29</definedName>
+    <definedName name="p_FRH">'Paramètres'!$C$25</definedName>
+    <definedName name="p_PROP">'Paramètres'!$C$26</definedName>
+    <definedName name="p_SFB">'Paramètres'!$C$27</definedName>
+    <definedName name="p_SFH">'Paramètres'!$C$28</definedName>
+    <definedName name="p_FRL">'Paramètres'!$C$29</definedName>
     <definedName name="p_SIA">'Paramètres'!$C$30</definedName>
     <definedName name="p_SIH">'Paramètres'!$C$31</definedName>
     <definedName name="p_FPA">'Paramètres'!$C$32</definedName>
@@ -101,49 +101,50 @@
     <definedName name="px_gravier">'Prix'!$D$8</definedName>
     <definedName name="px_eau">'Prix'!$D$9</definedName>
     <definedName name="px_agglo">'Prix'!$D$10</definedName>
-    <definedName name="px_ha6">'Prix'!$D$11</definedName>
-    <definedName name="px_ha10">'Prix'!$D$12</definedName>
-    <definedName name="px_ha12">'Prix'!$D$13</definedName>
-    <definedName name="px_fil">'Prix'!$D$14</definedName>
-    <definedName name="px_bois">'Prix'!$D$15</definedName>
-    <definedName name="px_pointes">'Prix'!$D$16</definedName>
-    <definedName name="px_huile">'Prix'!$D$17</definedName>
-    <definedName name="px_hydro">'Prix'!$D$18</definedName>
-    <definedName name="px_termite">'Prix'!$D$19</definedName>
-    <definedName name="px_laterite">'Prix'!$D$20</definedName>
-    <definedName name="px_polyane">'Prix'!$D$21</definedName>
-    <definedName name="px_joint">'Prix'!$D$22</definedName>
-    <definedName name="px_ipe">'Prix'!$D$23</definedName>
-    <definedName name="px_corniere">'Prix'!$D$24</definedName>
-    <definedName name="px_tole">'Prix'!$D$25</definedName>
-    <definedName name="px_tige">'Prix'!$D$26</definedName>
-    <definedName name="px_grout">'Prix'!$D$27</definedName>
-    <definedName name="px_peint">'Prix'!$D$28</definedName>
-    <definedName name="px_acier_ch">'Prix'!$D$29</definedName>
-    <definedName name="px_bac">'Prix'!$D$30</definedName>
-    <definedName name="px_zpanne">'Prix'!$D$31</definedName>
-    <definedName name="px_faitiere">'Prix'!$D$32</definedName>
-    <definedName name="px_ff_install">'Prix'!$D$33</definedName>
-    <definedName name="px_ff_implant">'Prix'!$D$34</definedName>
-    <definedName name="px_ff_essais">'Prix'!$D$35</definedName>
-    <definedName name="px_ff_portail">'Prix'!$D$36</definedName>
-    <definedName name="px_mo_macon">'Prix'!$D$38</definedName>
-    <definedName name="px_mo_ferr">'Prix'!$D$39</definedName>
-    <definedName name="px_mo_coff">'Prix'!$D$40</definedName>
-    <definedName name="px_mo_soud">'Prix'!$D$41</definedName>
-    <definedName name="px_mo_tech">'Prix'!$D$42</definedName>
-    <definedName name="px_mo_man">'Prix'!$D$43</definedName>
-    <definedName name="px_mt_bet">'Prix'!$D$45</definedName>
-    <definedName name="px_mt_vib">'Prix'!$D$46</definedName>
-    <definedName name="px_mt_dame">'Prix'!$D$47</definedName>
-    <definedName name="px_mt_plaque">'Prix'!$D$48</definedName>
-    <definedName name="px_mt_cam">'Prix'!$D$49</definedName>
-    <definedName name="px_mt_scie">'Prix'!$D$50</definedName>
-    <definedName name="px_mt_niveau">'Prix'!$D$51</definedName>
-    <definedName name="px_mt_branch">'Prix'!$D$52</definedName>
-    <definedName name="px_mt_ch">'Prix'!$D$53</definedName>
-    <definedName name="px_mt_echaf">'Prix'!$D$54</definedName>
-    <definedName name="px_mt_portail">'Prix'!$D$55</definedName>
+    <definedName name="px_agglo_cr">'Prix'!$D$11</definedName>
+    <definedName name="px_ha6">'Prix'!$D$12</definedName>
+    <definedName name="px_ha10">'Prix'!$D$13</definedName>
+    <definedName name="px_ha12">'Prix'!$D$14</definedName>
+    <definedName name="px_fil">'Prix'!$D$15</definedName>
+    <definedName name="px_bois">'Prix'!$D$16</definedName>
+    <definedName name="px_pointes">'Prix'!$D$17</definedName>
+    <definedName name="px_huile">'Prix'!$D$18</definedName>
+    <definedName name="px_hydro">'Prix'!$D$19</definedName>
+    <definedName name="px_termite">'Prix'!$D$20</definedName>
+    <definedName name="px_laterite">'Prix'!$D$21</definedName>
+    <definedName name="px_polyane">'Prix'!$D$22</definedName>
+    <definedName name="px_joint">'Prix'!$D$23</definedName>
+    <definedName name="px_ipe">'Prix'!$D$24</definedName>
+    <definedName name="px_corniere">'Prix'!$D$25</definedName>
+    <definedName name="px_tole">'Prix'!$D$26</definedName>
+    <definedName name="px_tige">'Prix'!$D$27</definedName>
+    <definedName name="px_grout">'Prix'!$D$28</definedName>
+    <definedName name="px_peint">'Prix'!$D$29</definedName>
+    <definedName name="px_acier_ch">'Prix'!$D$30</definedName>
+    <definedName name="px_bac">'Prix'!$D$31</definedName>
+    <definedName name="px_zpanne">'Prix'!$D$32</definedName>
+    <definedName name="px_faitiere">'Prix'!$D$33</definedName>
+    <definedName name="px_ff_install">'Prix'!$D$34</definedName>
+    <definedName name="px_ff_implant">'Prix'!$D$35</definedName>
+    <definedName name="px_ff_essais">'Prix'!$D$36</definedName>
+    <definedName name="px_ff_portail">'Prix'!$D$37</definedName>
+    <definedName name="px_mo_macon">'Prix'!$D$39</definedName>
+    <definedName name="px_mo_ferr">'Prix'!$D$40</definedName>
+    <definedName name="px_mo_coff">'Prix'!$D$41</definedName>
+    <definedName name="px_mo_soud">'Prix'!$D$42</definedName>
+    <definedName name="px_mo_tech">'Prix'!$D$43</definedName>
+    <definedName name="px_mo_man">'Prix'!$D$44</definedName>
+    <definedName name="px_mt_bet">'Prix'!$D$46</definedName>
+    <definedName name="px_mt_vib">'Prix'!$D$47</definedName>
+    <definedName name="px_mt_dame">'Prix'!$D$48</definedName>
+    <definedName name="px_mt_plaque">'Prix'!$D$49</definedName>
+    <definedName name="px_mt_cam">'Prix'!$D$50</definedName>
+    <definedName name="px_mt_scie">'Prix'!$D$51</definedName>
+    <definedName name="px_mt_niveau">'Prix'!$D$52</definedName>
+    <definedName name="px_mt_branch">'Prix'!$D$53</definedName>
+    <definedName name="px_mt_ch">'Prix'!$D$54</definedName>
+    <definedName name="px_mt_echaf">'Prix'!$D$55</definedName>
+    <definedName name="px_mt_portail">'Prix'!$D$56</definedName>
     <definedName name="q_0_1">'Métré'!$F$6</definedName>
     <definedName name="q_0_2">'Métré'!$F$7</definedName>
     <definedName name="q_0_3">'Métré'!$F$8</definedName>
@@ -966,7 +967,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Métré, déboursé sec et devis quantitatif et estimatif (DQE) d'un bâtiment industriel 30 x 10 m, murs en agglos 15 pleins, piliers IPE 220 tous les 5 m encadrés de 2 poteaux BA, contreventements en cornières 50x50x5, entrée 6 m, toiture 2 versants à 20 %, dallage BA 20 cm double nappe HA10, semelles isolées 80 x 80 x 30 en HA12 avec tiges d'ancrage.</t>
+          <t>Métré, déboursé sec et devis quantitatif et estimatif (DQE) d'un bâtiment industriel 30 x 10 m, murs en agglos 15 pleins en fondation (1 m) et 15 creux en élévation (6 m), semelle filante 60 x 15, piliers IPE 220 tous les 5 m encadrés de 2 poteaux BA, contreventements en cornières 50x50x5, entrée 6 m, toiture 2 versants à 20 %, dallage BA 20 cm nappe simple HA10, semelles isolées 80 x 80 x 30 en HA12 avec tiges d'ancrage.</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1231,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>20 cm, béton dosé à 350 kg/m³, double nappe HA10 e = 20 cm, chaises HA10, polyane, joints sciés maille 5 m.</t>
+          <t>20 cm, béton dosé à 350 kg/m³, nappe simple HA10 e = 20 cm (p_NNAP = 2 pour double nappe), chaises HA10, polyane, joints sciés maille 5 m.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1500,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Épaisseur des murs (agglos 15 pleins)</t>
+          <t>Épaisseur des murs (agglos 15)</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -1799,111 +1800,124 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>p_FRL</t>
+          <t>p_FRH</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Largeur des fouilles en rigole</t>
+          <t>Profondeur des fouilles (rigoles et puits)</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Donnée : 120 cm</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>p_FRH</t>
+          <t>p_PROP</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Profondeur des fouilles (rigoles et puits)</t>
+          <t>Épaisseur béton de propreté</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1.2</v>
+        <v>0.05</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Donnée : 120 cm</t>
-        </is>
-      </c>
+      <c r="E26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>p_PROP</t>
+          <t>p_SFB</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Épaisseur béton de propreté</t>
+          <t>Semelle filante : largeur</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Donnée : 60 cm</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>p_SFB</t>
+          <t>p_SFH</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Semelle filante : largeur</t>
+          <t>Semelle filante : hauteur</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Donnée : 15 cm</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>p_SFH</t>
+          <t>p_FRL</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Semelle filante : hauteur</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>0.15</v>
+          <t>Largeur des fouilles en rigole</t>
+        </is>
+      </c>
+      <c r="C29" s="13">
+        <f>p_SFB+0.20</f>
+        <v>0.8</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Semelle + 10 cm de chaque côté</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -2146,7 +2160,7 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -2155,7 +2169,7 @@
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Donnée : double nappe HA10</t>
+          <t>Donnée : nappe simple HA10 (mettre 2 pour une double nappe)</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3135,7 @@
       </c>
       <c r="C85" s="13">
         <f>p_P*p_FRL*p_FRH</f>
-        <v>57.599999999999994</v>
+        <v>76.8</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
@@ -3143,7 +3157,7 @@
       </c>
       <c r="C86" s="13">
         <f>p_NPIL*(p_FPA*p_FPA-p_FRL*p_FPA)*p_FRH</f>
-        <v>8.16</v>
+        <v>4.079999999999999</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
@@ -3165,7 +3179,7 @@
       </c>
       <c r="C87" s="13">
         <f>(p_P-p_NPIL*p_FPA)*p_FRL*p_PROP+p_NPIL*p_FPA*p_FPA*p_PROP</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
@@ -3209,7 +3223,7 @@
       </c>
       <c r="C89" s="13">
         <f>(p_P-p_NPIL*p_SIA)*p_SFB*p_SFH</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
@@ -3231,7 +3245,7 @@
       </c>
       <c r="C90" s="13">
         <f>p_VPROP+p_VSI+p_VSF+p_LNET*p_HFOND*p_EP+p_NPIL*(p_AFUT*p_AFUT+p_NPO*p_APO*p_APO)*p_HENT</f>
-        <v>23.904750000000003</v>
+        <v>26.526750000000003</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
@@ -3260,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3450,21 +3464,21 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>ha6</t>
+          <t>agglo_cr</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Acier HA6 FeE500 (barre 12 m = 2,66 kg à 2 300)</t>
+          <t>Agglo 15 creux 40x20x15 rendu chantier</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>865</v>
+        <v>400</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
@@ -3475,12 +3489,12 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>ha10</t>
+          <t>ha6</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Acier HA10 FeE500 (barre 12 m = 7,40 kg à 6 000)</t>
+          <t>Acier HA6 FeE500 (barre 12 m = 2,66 kg à 2 300)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -3489,7 +3503,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>810</v>
+        <v>865</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -3500,12 +3514,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>ha12</t>
+          <t>ha10</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Acier HA12 FeE500 (barre 12 m = 10,66 kg à 8 500)</t>
+          <t>Acier HA10 FeE500 (barre 12 m = 7,40 kg à 6 000)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -3514,7 +3528,7 @@
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
@@ -3525,12 +3539,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>ha12</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Fil recuit</t>
+          <t>Acier HA12 FeE500 (barre 12 m = 10,66 kg à 8 500)</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3539,7 +3553,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -3550,21 +3564,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>bois</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Bois de coffrage (amorti 3 emplois)</t>
+          <t>Fil recuit</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
@@ -3575,21 +3589,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>pointes</t>
+          <t>bois</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Pointes</t>
+          <t>Bois de coffrage (amorti 3 emplois)</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -3600,21 +3614,21 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>huile</t>
+          <t>pointes</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Huile de décoffrage</t>
+          <t>Pointes</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
@@ -3625,12 +3639,12 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>hydro</t>
+          <t>huile</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Hydrofuge de masse</t>
+          <t>Huile de décoffrage</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -3639,7 +3653,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -3650,21 +3664,21 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>termite</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Produit anti-termites (dilué)</t>
+          <t>Hydrofuge de masse</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
@@ -3675,21 +3689,21 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>laterite</t>
+          <t>termite</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Latérite d'emprunt rendue chantier</t>
+          <t>Produit anti-termites (dilué)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
@@ -3700,21 +3714,21 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>polyane</t>
+          <t>laterite</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Film polyane 150 µ</t>
+          <t>Latérite d'emprunt rendue chantier</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
@@ -3725,21 +3739,21 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>polyane</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Fond de joint + mastic / joint périphérique</t>
+          <t>Film polyane 150 µ</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -3750,21 +3764,21 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>ipe</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Profilé IPE 220 (S235)</t>
+          <t>Fond de joint + mastic / joint périphérique</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
@@ -3775,12 +3789,12 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>corniere</t>
+          <t>ipe</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Cornière 50x50x5 (S235)</t>
+          <t>Profilé IPE 220 (S235)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -3789,7 +3803,7 @@
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -3800,12 +3814,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>tole</t>
+          <t>corniere</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Tôle pour platines et goussets ép. 15 mm</t>
+          <t>Cornière 50x50x5 (S235)</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -3825,21 +3839,21 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>tige</t>
+          <t>tole</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Tige d'ancrage M20 L = 600 coudée + 2 écrous + rondelle</t>
+          <t>Tôle pour platines et goussets ép. 15 mm</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>6000</v>
+        <v>900</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3850,21 +3864,21 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>grout</t>
+          <t>tige</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Mortier de calage sans retrait (sac 25 kg)</t>
+          <t>Tige d'ancrage M20 L = 600 coudée + 2 écrous + rondelle</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
@@ -3875,21 +3889,21 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>peint</t>
+          <t>grout</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Peinture antirouille + finition (2 couches)</t>
+          <t>Mortier de calage sans retrait (sac 25 kg)</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sac</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>100</v>
+        <v>9000</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -3900,12 +3914,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>acier_ch</t>
+          <t>peint</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Profilés charpente de toiture + peinture</t>
+          <t>Peinture antirouille + finition (2 couches)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -3914,7 +3928,7 @@
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
@@ -3925,21 +3939,21 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>bac</t>
+          <t>acier_ch</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Tôle bac 5 ondes (alu 6/10 ou acier prélaqué) + fixations</t>
+          <t>Profilés charpente de toiture + peinture</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>4500</v>
+        <v>950</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
@@ -3950,21 +3964,21 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>zpanne</t>
+          <t>bac</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Panne Z 120 x 2 galvanisée + échantignoles + boulons</t>
+          <t>Tôle bac 5 ondes (alu 6/10 ou acier prélaqué) + fixations</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
@@ -3975,21 +3989,21 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>faitiere</t>
+          <t>zpanne</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Faîtière aluminium</t>
+          <t>Panne Z 120 x 2 galvanisée + échantignoles + boulons</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
@@ -4000,21 +4014,21 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>ff_install</t>
+          <t>faitiere</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Magasin, clôture provisoire, panneau de chantier</t>
+          <t>Faîtière aluminium</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
-        <v>300000</v>
+        <v>3500</v>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
@@ -4025,12 +4039,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>ff_implant</t>
+          <t>ff_install</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Bois de chaises, cordeau, peinture</t>
+          <t>Magasin, clôture provisoire, panneau de chantier</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -4039,7 +4053,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
@@ -4050,12 +4064,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>ff_essais</t>
+          <t>ff_implant</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Essais labo (Proctor, densités in situ, écrasement béton)</t>
+          <t>Bois de chaises, cordeau, peinture</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -4064,7 +4078,7 @@
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>250000</v>
+        <v>40000</v>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
@@ -4075,73 +4089,73 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
+          <t>ff_essais</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Essais labo (Proctor, densités in situ, écrasement béton)</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Matériaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
           <t>ff_portail</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Portail : tubes, tôle 15/10, rail, roulettes, peinture</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>ft</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D37" s="16" t="n">
         <v>1600000</v>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Matériaux</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>MAIN-D'ŒUVRE</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>mo_macon</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Maçon</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>h.j</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Main-d'œuvre</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>mo_ferr</t>
+          <t>mo_macon</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Ferrailleur</t>
+          <t>Maçon</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -4161,12 +4175,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>mo_coff</t>
+          <t>mo_ferr</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Coffreur</t>
+          <t>Ferrailleur</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -4186,12 +4200,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>mo_soud</t>
+          <t>mo_coff</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Soudeur / couvreur</t>
+          <t>Coffreur</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -4200,7 +4214,7 @@
         </is>
       </c>
       <c r="D41" s="16" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
@@ -4211,12 +4225,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>mo_tech</t>
+          <t>mo_soud</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Technicien</t>
+          <t>Soudeur / couvreur</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -4236,73 +4250,73 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
+          <t>mo_tech</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Technicien</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>h.j</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Main-d'œuvre</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
           <t>mo_man</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Manœuvre</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>h.j</t>
         </is>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D44" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Main-d'œuvre</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>MATÉRIEL</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>mt_bet</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Bétonnière 350 L (location)</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>j</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>mt_vib</t>
+          <t>mt_bet</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Vibreur (location)</t>
+          <t>Bétonnière 350 L (location)</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -4311,7 +4325,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
@@ -4322,12 +4336,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>mt_dame</t>
+          <t>mt_vib</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Dame sauteuse (location)</t>
+          <t>Vibreur (location)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -4336,7 +4350,7 @@
         </is>
       </c>
       <c r="D47" s="16" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
@@ -4347,12 +4361,12 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>mt_plaque</t>
+          <t>mt_dame</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Compacteur à plaque vibrante / rouleau 1 t (location)</t>
+          <t>Dame sauteuse (location)</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -4361,7 +4375,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
@@ -4372,21 +4386,21 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>mt_cam</t>
+          <t>mt_plaque</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Camion benne 10 m³</t>
+          <t>Compacteur à plaque vibrante / rouleau 1 t (location)</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>voyage</t>
+          <t>j</t>
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
@@ -4397,21 +4411,21 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>mt_scie</t>
+          <t>mt_cam</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Scie à sol (location)</t>
+          <t>Camion benne 10 m³</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>voyage</t>
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
@@ -4422,12 +4436,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>mt_niveau</t>
+          <t>mt_scie</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Niveau / théodolite (location)</t>
+          <t>Scie à sol (location)</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -4436,7 +4450,7 @@
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
@@ -4447,21 +4461,21 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>mt_branch</t>
+          <t>mt_niveau</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Branchements provisoires eau et électricité</t>
+          <t>Niveau / théodolite (location)</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>j</t>
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>100000</v>
+        <v>15000</v>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
@@ -4472,21 +4486,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>mt_ch</t>
+          <t>mt_branch</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Poste à souder, meuleuse, levage (charpente)</t>
+          <t>Branchements provisoires eau et électricité</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="D53" s="16" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
@@ -4497,21 +4511,21 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>mt_echaf</t>
+          <t>mt_ch</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Échafaudage (location)</t>
+          <t>Poste à souder, meuleuse, levage (charpente)</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
@@ -4522,30 +4536,55 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
+          <t>mt_echaf</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Échafaudage (location)</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Matériel</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
           <t>mt_portail</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>Poste à souder, meuleuse (portail)</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>ft</t>
         </is>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D56" s="16" t="n">
         <v>150000</v>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>Matériel</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="17" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>Source : estimation du marché d'Abidjan, octobre 2026 - à actualiser avec les cotations des fournisseurs.</t>
         </is>
@@ -4753,7 +4792,7 @@
       </c>
       <c r="D9" s="18">
         <f>p_P/0.20*(p_SFB+0.05)</f>
-        <v>180.0</v>
+        <v>260.0</v>
       </c>
       <c r="E9" s="19">
         <f>p_KG6</f>
@@ -4761,7 +4800,7 @@
       </c>
       <c r="F9" s="18">
         <f>D9*E9</f>
-        <v>39.96</v>
+        <v>57.72</v>
       </c>
     </row>
     <row r="10">
@@ -5094,7 +5133,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Dallage : double nappe HA10 e=20 dans les 2 sens</t>
+          <t>Dallage : nappe(s) HA10 e=20 dans les 2 sens</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -5104,7 +5143,7 @@
       </c>
       <c r="D22" s="18">
         <f>p_SINT*p_NNAP*2/p_EDAL*p_RDAL</f>
-        <v>6468.494999999999</v>
+        <v>3234.2474999999995</v>
       </c>
       <c r="E22" s="19">
         <f>p_KG10</f>
@@ -5112,7 +5151,7 @@
       </c>
       <c r="F22" s="18">
         <f>D22*E22</f>
-        <v>3991.061414999999</v>
+        <v>1995.5307074999996</v>
       </c>
     </row>
     <row r="23">
@@ -5257,7 +5296,7 @@
       </c>
       <c r="D28" s="18">
         <f>SUMIFS('Aciers'!$F$5:$F$23,'Aciers'!$A$5:$A$23,A28,'Aciers'!$C$5:$C$23,C28)</f>
-        <v>130.2252</v>
+        <v>147.9852</v>
       </c>
       <c r="E28" s="21">
         <f>p_CHUTES</f>
@@ -5265,11 +5304,11 @@
       </c>
       <c r="F28" s="18">
         <f>D28*E28</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="G28" s="22">
         <f>ROUNDUP(F28/(12*p_KG6),0)</f>
-        <v>52.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="29">
@@ -5350,7 +5389,7 @@
       </c>
       <c r="D31" s="18">
         <f>SUMIFS('Aciers'!$F$5:$F$23,'Aciers'!$A$5:$A$23,A31,'Aciers'!$C$5:$C$23,C31)</f>
-        <v>4136.190920999999</v>
+        <v>2140.6602134999994</v>
       </c>
       <c r="E31" s="21">
         <f>p_CHUTES</f>
@@ -5358,11 +5397,11 @@
       </c>
       <c r="F31" s="18">
         <f>D31*E31</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="G31" s="22">
         <f>ROUNDUP(F31/(12*p_KG10),0)</f>
-        <v>587.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="32">
@@ -5408,7 +5447,7 @@
       </c>
       <c r="D33" s="25">
         <f>SUMIFS('Aciers'!$F$5:$F$23,'Aciers'!$C$5:$C$23,C33)</f>
-        <v>5706.173793702006</v>
+        <v>3710.643086202006</v>
       </c>
       <c r="E33" s="26">
         <f>p_CHUTES</f>
@@ -5416,11 +5455,11 @@
       </c>
       <c r="F33" s="25">
         <f>D33*E33</f>
-        <v>5991.482483387107</v>
+        <v>3896.1752405121065</v>
       </c>
       <c r="G33" s="27">
         <f>ROUNDUP(F33/(12*p_KG10),0)</f>
-        <v>810.0</v>
+        <v>527.0</v>
       </c>
     </row>
     <row r="34">
@@ -5437,7 +5476,7 @@
       </c>
       <c r="D34" s="25">
         <f>SUMIFS('Aciers'!$F$5:$F$23,'Aciers'!$C$5:$C$23,C34)</f>
-        <v>431.699023320176</v>
+        <v>449.459023320176</v>
       </c>
       <c r="E34" s="26">
         <f>p_CHUTES</f>
@@ -5445,11 +5484,11 @@
       </c>
       <c r="F34" s="25">
         <f>D34*E34</f>
-        <v>453.28397448618483</v>
+        <v>471.93197448618486</v>
       </c>
       <c r="G34" s="27">
         <f>ROUNDUP(F34/(12*p_KG6),0)</f>
-        <v>171.0</v>
+        <v>178.0</v>
       </c>
     </row>
   </sheetData>
@@ -5659,7 +5698,7 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>Fouilles en rigole 0,60 x 1,20 m en terrain latéritique</t>
+          <t>Fouilles en rigole 0,80 x 1,20 m en terrain latéritique</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -5674,7 +5713,7 @@
       </c>
       <c r="F10" s="18">
         <f>p_VRIG</f>
-        <v>57.599999999999994</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="11">
@@ -5703,7 +5742,7 @@
       </c>
       <c r="F11" s="18">
         <f>p_VPUI</f>
-        <v>8.16</v>
+        <v>4.079999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -5732,7 +5771,7 @@
       </c>
       <c r="F12" s="18">
         <f>p_VRIG+p_VPUI-p_VENT</f>
-        <v>41.855249999999984</v>
+        <v>54.35324999999999</v>
       </c>
     </row>
     <row r="13">
@@ -5761,7 +5800,7 @@
       </c>
       <c r="F13" s="18">
         <f>p_VENT*p_FOIS</f>
-        <v>29.880937500000005</v>
+        <v>33.158437500000005</v>
       </c>
     </row>
     <row r="14">
@@ -5790,7 +5829,7 @@
       </c>
       <c r="F14" s="18">
         <f>p_P*p_FRL+p_NPIL*(p_FPA*p_FPA-p_FRL*p_FPA)</f>
-        <v>54.8</v>
+        <v>67.4</v>
       </c>
     </row>
     <row r="15">
@@ -5835,7 +5874,7 @@
       </c>
       <c r="F16" s="18">
         <f>p_VPROP</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
     </row>
     <row r="17">
@@ -5936,7 +5975,7 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>Béton armé dosé à 350 kg/m³ pour semelle filante 0,40 x 0,15</t>
+          <t>Béton armé dosé à 350 kg/m³ pour semelle filante 0,60 x 0,15</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -5951,7 +5990,7 @@
       </c>
       <c r="F20" s="18">
         <f>p_VSF</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
     </row>
     <row r="21">
@@ -6154,7 +6193,7 @@
       </c>
       <c r="F27" s="18">
         <f>'Aciers'!$F$28</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
     </row>
     <row r="28">
@@ -6184,7 +6223,7 @@
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>Maçonnerie d'agglos 15 pleins en élévation, mortier dosé à 300 kg/m³ (y compris pignons)</t>
+          <t>Maçonnerie d'agglos 15 creux en élévation h = 6,00 m, mortier dosé à 300 kg/m³ (y compris pignons)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -6738,7 +6777,7 @@
       </c>
       <c r="C49" s="28" t="inlineStr">
         <is>
-          <t>Armatures HA10 FeE500 - dallage double nappe e = 20 cm + chaises</t>
+          <t>Armatures HA10 FeE500 - dallage nappe simple e = 20 cm + chaises</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -6753,7 +6792,7 @@
       </c>
       <c r="F49" s="18">
         <f>'Aciers'!$F$31</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
     </row>
     <row r="50">
@@ -7788,7 +7827,7 @@
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Article 1.1 - Fouilles en rigole 0,60 x 1,20 m en terrain latéritique (unité : m³)</t>
+          <t>Article 1.1 - Fouilles en rigole 0,80 x 1,20 m en terrain latéritique (unité : m³)</t>
         </is>
       </c>
       <c r="C25" s="29" t="n"/>
@@ -7841,11 +7880,11 @@
       </c>
       <c r="I26" s="18">
         <f>q_1_1</f>
-        <v>57.599999999999994</v>
+        <v>76.8</v>
       </c>
       <c r="J26" s="18">
         <f>F26*I26</f>
-        <v>38.39999999999999</v>
+        <v>51.199999999999996</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -7968,11 +8007,11 @@
       </c>
       <c r="I31" s="18">
         <f>q_1_2</f>
-        <v>8.16</v>
+        <v>4.079999999999999</v>
       </c>
       <c r="J31" s="18">
         <f>F31*I31</f>
-        <v>5.4399999999999995</v>
+        <v>2.7199999999999993</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -8095,11 +8134,11 @@
       </c>
       <c r="I36" s="18">
         <f>q_1_3</f>
-        <v>41.855249999999984</v>
+        <v>54.35324999999999</v>
       </c>
       <c r="J36" s="18">
         <f>F36*I36</f>
-        <v>10.463812499999996</v>
+        <v>13.588312499999997</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -8147,11 +8186,11 @@
       </c>
       <c r="I37" s="18">
         <f>q_1_3</f>
-        <v>41.855249999999984</v>
+        <v>54.35324999999999</v>
       </c>
       <c r="J37" s="18">
         <f>F37*I37</f>
-        <v>2.092762499999999</v>
+        <v>2.7176624999999994</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -8274,11 +8313,11 @@
       </c>
       <c r="I42" s="18">
         <f>q_1_4</f>
-        <v>29.880937500000005</v>
+        <v>33.158437500000005</v>
       </c>
       <c r="J42" s="18">
         <f>F42*I42</f>
-        <v>5.976187500000002</v>
+        <v>6.631687500000002</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -8326,11 +8365,11 @@
       </c>
       <c r="I43" s="18">
         <f>q_1_4</f>
-        <v>29.880937500000005</v>
+        <v>33.158437500000005</v>
       </c>
       <c r="J43" s="18">
         <f>F43*I43</f>
-        <v>2.988093750000001</v>
+        <v>3.315843750000001</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -8453,11 +8492,11 @@
       </c>
       <c r="I48" s="18">
         <f>q_1_5</f>
-        <v>54.8</v>
+        <v>67.4</v>
       </c>
       <c r="J48" s="18">
         <f>F48*I48</f>
-        <v>54.8</v>
+        <v>67.4</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -8505,11 +8544,11 @@
       </c>
       <c r="I49" s="18">
         <f>q_1_5</f>
-        <v>54.8</v>
+        <v>67.4</v>
       </c>
       <c r="J49" s="18">
         <f>F49*I49</f>
-        <v>2.1919999999999997</v>
+        <v>2.696</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -8632,11 +8671,11 @@
       </c>
       <c r="I54" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J54" s="18">
         <f>F54*I54</f>
-        <v>8.22</v>
+        <v>10.110000000000001</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -8684,11 +8723,11 @@
       </c>
       <c r="I55" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J55" s="18">
         <f>F55*I55</f>
-        <v>1.233</v>
+        <v>1.5165000000000002</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -8736,11 +8775,11 @@
       </c>
       <c r="I56" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J56" s="18">
         <f>F56*I56</f>
-        <v>2.329</v>
+        <v>2.8645000000000005</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -8788,11 +8827,11 @@
       </c>
       <c r="I57" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J57" s="18">
         <f>F57*I57</f>
-        <v>0.548</v>
+        <v>0.6740000000000002</v>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
@@ -8840,11 +8879,11 @@
       </c>
       <c r="I58" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J58" s="18">
         <f>F58*I58</f>
-        <v>0.3425</v>
+        <v>0.42125000000000007</v>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
@@ -8892,11 +8931,11 @@
       </c>
       <c r="I59" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J59" s="18">
         <f>F59*I59</f>
-        <v>2.055</v>
+        <v>2.5275000000000003</v>
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
@@ -8944,11 +8983,11 @@
       </c>
       <c r="I60" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J60" s="18">
         <f>F60*I60</f>
-        <v>0.3425</v>
+        <v>0.42125000000000007</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -8996,11 +9035,11 @@
       </c>
       <c r="I61" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="J61" s="18">
         <f>F61*I61</f>
-        <v>0.3425</v>
+        <v>0.42125000000000007</v>
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
@@ -10335,7 +10374,7 @@
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Article 2.5 - Béton armé dosé à 350 kg/m³ pour semelle filante 0,40 x 0,15 (unité : m³)</t>
+          <t>Article 2.5 - Béton armé dosé à 350 kg/m³ pour semelle filante 0,60 x 0,15 (unité : m³)</t>
         </is>
       </c>
       <c r="C97" s="29" t="n"/>
@@ -10388,11 +10427,11 @@
       </c>
       <c r="I98" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J98" s="18">
         <f>F98*I98</f>
-        <v>27.887999999999998</v>
+        <v>41.832</v>
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
@@ -10440,11 +10479,11 @@
       </c>
       <c r="I99" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J99" s="18">
         <f>F99*I99</f>
-        <v>1.7928</v>
+        <v>2.6892</v>
       </c>
       <c r="K99" s="12" t="inlineStr">
         <is>
@@ -10492,11 +10531,11 @@
       </c>
       <c r="I100" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J100" s="18">
         <f>F100*I100</f>
-        <v>3.3864</v>
+        <v>5.0796</v>
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
@@ -10544,11 +10583,11 @@
       </c>
       <c r="I101" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J101" s="18">
         <f>F101*I101</f>
-        <v>0.7968000000000001</v>
+        <v>1.1952</v>
       </c>
       <c r="K101" s="12" t="inlineStr">
         <is>
@@ -10596,11 +10635,11 @@
       </c>
       <c r="I102" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J102" s="18">
         <f>F102*I102</f>
-        <v>0.6639999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
@@ -10648,11 +10687,11 @@
       </c>
       <c r="I103" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J103" s="18">
         <f>F103*I103</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="K103" s="12" t="inlineStr">
         <is>
@@ -10700,11 +10739,11 @@
       </c>
       <c r="I104" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J104" s="18">
         <f>F104*I104</f>
-        <v>0.6639999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
@@ -10752,11 +10791,11 @@
       </c>
       <c r="I105" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="J105" s="18">
         <f>F105*I105</f>
-        <v>0.6639999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="K105" s="12" t="inlineStr">
         <is>
@@ -12993,11 +13032,11 @@
       </c>
       <c r="I166" s="18">
         <f>q_2_12</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="J166" s="18">
         <f>F166*I166</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="K166" s="12" t="inlineStr">
         <is>
@@ -13045,11 +13084,11 @@
       </c>
       <c r="I167" s="18">
         <f>q_2_12</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="J167" s="18">
         <f>F167*I167</f>
-        <v>2.0510469</v>
+        <v>2.3307669</v>
       </c>
       <c r="K167" s="12" t="inlineStr">
         <is>
@@ -13097,11 +13136,11 @@
       </c>
       <c r="I168" s="18">
         <f>q_2_12</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="J168" s="18">
         <f>F168*I168</f>
-        <v>0.9115764000000001</v>
+        <v>1.0358964</v>
       </c>
       <c r="K168" s="12" t="inlineStr">
         <is>
@@ -13149,11 +13188,11 @@
       </c>
       <c r="I169" s="18">
         <f>q_2_12</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="J169" s="18">
         <f>F169*I169</f>
-        <v>0.9115764000000001</v>
+        <v>1.0358964</v>
       </c>
       <c r="K169" s="12" t="inlineStr">
         <is>
@@ -13223,7 +13262,7 @@
       <c r="A173" s="8" t="n"/>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>Article 3.1 - Maçonnerie d'agglos 15 pleins en élévation, mortier dosé à 300 kg/m³ (y compris pignons) (unité : m²)</t>
+          <t>Article 3.1 - Maçonnerie d'agglos 15 creux en élévation h = 6,00 m, mortier dosé à 300 kg/m³ (y compris pignons) (unité : m²)</t>
         </is>
       </c>
       <c r="C173" s="29" t="n"/>
@@ -13249,12 +13288,12 @@
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>Agglos 15 pleins (12,5 u/m² + 5 % casse)</t>
+          <t>Agglos 15 creux (12,5 u/m² + 5 % casse)</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>agglo</t>
+          <t>agglo_cr</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
@@ -13267,12 +13306,12 @@
         <v>13.125</v>
       </c>
       <c r="G174" s="32">
-        <f>px_agglo</f>
-        <v>500.0</v>
+        <f>px_agglo_cr</f>
+        <v>400.0</v>
       </c>
       <c r="H174" s="32">
         <f>F174*G174</f>
-        <v>6562.5</v>
+        <v>5250.0</v>
       </c>
       <c r="I174" s="18">
         <f>q_3_1</f>
@@ -13315,8 +13354,8 @@
         </is>
       </c>
       <c r="F175" s="31">
-        <f>0.15</f>
-        <v>0.15</v>
+        <f>0.13</f>
+        <v>0.13</v>
       </c>
       <c r="G175" s="32">
         <f>px_ciment</f>
@@ -13324,7 +13363,7 @@
       </c>
       <c r="H175" s="32">
         <f>F175*G175</f>
-        <v>870.0</v>
+        <v>754.0</v>
       </c>
       <c r="I175" s="18">
         <f>q_3_1</f>
@@ -13332,7 +13371,7 @@
       </c>
       <c r="J175" s="18">
         <f>F175*I175</f>
-        <v>56.08388824377665</v>
+        <v>48.60603647793977</v>
       </c>
       <c r="K175" s="12" t="inlineStr">
         <is>
@@ -13367,8 +13406,8 @@
         </is>
       </c>
       <c r="F176" s="31">
-        <f>0.03</f>
-        <v>0.03</v>
+        <f>0.025</f>
+        <v>0.025</v>
       </c>
       <c r="G176" s="32">
         <f>px_sable</f>
@@ -13376,7 +13415,7 @@
       </c>
       <c r="H176" s="32">
         <f>F176*G176</f>
-        <v>360.0</v>
+        <v>300.0</v>
       </c>
       <c r="I176" s="18">
         <f>q_3_1</f>
@@ -13384,7 +13423,7 @@
       </c>
       <c r="J176" s="18">
         <f>F176*I176</f>
-        <v>11.216777648755329</v>
+        <v>9.347314707296109</v>
       </c>
       <c r="K176" s="12" t="inlineStr">
         <is>
@@ -13457,7 +13496,7 @@
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>Maçon (10 m²/j)</t>
+          <t>Maçon (12 m²/j)</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
@@ -13471,8 +13510,8 @@
         </is>
       </c>
       <c r="F178" s="31">
-        <f>1/10</f>
-        <v>0.1</v>
+        <f>1/12</f>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G178" s="32">
         <f>px_mo_macon</f>
@@ -13480,7 +13519,7 @@
       </c>
       <c r="H178" s="32">
         <f>F178*G178</f>
-        <v>1000.0</v>
+        <v>833.3333333333333</v>
       </c>
       <c r="I178" s="18">
         <f>q_3_1</f>
@@ -13488,7 +13527,7 @@
       </c>
       <c r="J178" s="18">
         <f>F178*I178</f>
-        <v>37.389258829184435</v>
+        <v>31.157715690987025</v>
       </c>
       <c r="K178" s="12" t="inlineStr">
         <is>
@@ -13509,7 +13548,7 @@
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Manœuvre (10 m²/j)</t>
+          <t>Manœuvre (12 m²/j)</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
@@ -13523,8 +13562,8 @@
         </is>
       </c>
       <c r="F179" s="31">
-        <f>1/10</f>
-        <v>0.1</v>
+        <f>1/12</f>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G179" s="32">
         <f>px_mo_man</f>
@@ -13532,7 +13571,7 @@
       </c>
       <c r="H179" s="32">
         <f>F179*G179</f>
-        <v>500.0</v>
+        <v>416.66666666666663</v>
       </c>
       <c r="I179" s="18">
         <f>q_3_1</f>
@@ -13540,7 +13579,7 @@
       </c>
       <c r="J179" s="18">
         <f>F179*I179</f>
-        <v>37.389258829184435</v>
+        <v>31.157715690987025</v>
       </c>
       <c r="K179" s="12" t="inlineStr">
         <is>
@@ -13576,11 +13615,11 @@
       </c>
       <c r="G180" s="32">
         <f>SUMIFS(H174:H179,B174:B179,"Main-d'œuvre")</f>
-        <v>1500.0</v>
+        <v>1250.0</v>
       </c>
       <c r="H180" s="32">
         <f>F180*G180</f>
-        <v>45.0</v>
+        <v>37.5</v>
       </c>
       <c r="I180" s="10" t="n"/>
       <c r="J180" s="10" t="n"/>
@@ -13600,7 +13639,7 @@
       <c r="G181" s="34" t="n"/>
       <c r="H181" s="36">
         <f>SUM(H174:H180)</f>
-        <v>9347.5</v>
+        <v>7601.5</v>
       </c>
       <c r="I181" s="34" t="n"/>
       <c r="J181" s="34" t="n"/>
@@ -19149,7 +19188,7 @@
       <c r="A333" s="8" t="n"/>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Article 5.6 - Armatures HA10 FeE500 - dallage double nappe e = 20 cm + chaises (unité : kg)</t>
+          <t>Article 5.6 - Armatures HA10 FeE500 - dallage nappe simple e = 20 cm + chaises (unité : kg)</t>
         </is>
       </c>
       <c r="C333" s="29" t="n"/>
@@ -19202,11 +19241,11 @@
       </c>
       <c r="I334" s="18">
         <f>q_5_6</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="J334" s="18">
         <f>F334*I334</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="K334" s="12" t="inlineStr">
         <is>
@@ -19254,11 +19293,11 @@
       </c>
       <c r="I335" s="18">
         <f>q_5_6</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="J335" s="18">
         <f>F335*I335</f>
-        <v>65.14500700574999</v>
+        <v>33.715398362624995</v>
       </c>
       <c r="K335" s="12" t="inlineStr">
         <is>
@@ -19306,11 +19345,11 @@
       </c>
       <c r="I336" s="18">
         <f>q_5_6</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="J336" s="18">
         <f>F336*I336</f>
-        <v>21.71500233525</v>
+        <v>11.238466120874998</v>
       </c>
       <c r="K336" s="12" t="inlineStr">
         <is>
@@ -19358,11 +19397,11 @@
       </c>
       <c r="I337" s="18">
         <f>q_5_6</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="J337" s="18">
         <f>F337*I337</f>
-        <v>21.71500233525</v>
+        <v>11.238466120874998</v>
       </c>
       <c r="K337" s="12" t="inlineStr">
         <is>
@@ -22223,7 +22262,7 @@
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>Fouilles en rigole 0,60 x 1,20 m en terrain latéritique</t>
+          <t>Fouilles en rigole 0,80 x 1,20 m en terrain latéritique</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -22233,7 +22272,7 @@
       </c>
       <c r="D12" s="18">
         <f>q_1_1</f>
-        <v>57.599999999999994</v>
+        <v>76.8</v>
       </c>
       <c r="E12" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A12,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -22257,15 +22296,15 @@
       </c>
       <c r="J12" s="32">
         <f>$D12*F12</f>
-        <v>191999.99999999997</v>
+        <v>255999.99999999997</v>
       </c>
       <c r="K12" s="32">
         <f>$D12*G12</f>
-        <v>5759.999999999998</v>
+        <v>7679.999999999998</v>
       </c>
       <c r="L12" s="32">
         <f>$D12*H12</f>
-        <v>197759.99999999997</v>
+        <v>263679.99999999994</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -22291,7 +22330,7 @@
       </c>
       <c r="D13" s="18">
         <f>q_1_2</f>
-        <v>8.16</v>
+        <v>4.079999999999999</v>
       </c>
       <c r="E13" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A13,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -22315,15 +22354,15 @@
       </c>
       <c r="J13" s="32">
         <f>$D13*F13</f>
-        <v>27199.999999999996</v>
+        <v>13599.999999999996</v>
       </c>
       <c r="K13" s="32">
         <f>$D13*G13</f>
-        <v>815.9999999999999</v>
+        <v>407.9999999999999</v>
       </c>
       <c r="L13" s="32">
         <f>$D13*H13</f>
-        <v>28015.999999999996</v>
+        <v>14007.999999999996</v>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
@@ -22349,7 +22388,7 @@
       </c>
       <c r="D14" s="18">
         <f>q_1_3</f>
-        <v>41.855249999999984</v>
+        <v>54.35324999999999</v>
       </c>
       <c r="E14" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A14,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -22373,15 +22412,15 @@
       </c>
       <c r="J14" s="32">
         <f>$D14*F14</f>
-        <v>52319.06249999998</v>
+        <v>67941.56249999999</v>
       </c>
       <c r="K14" s="32">
         <f>$D14*G14</f>
-        <v>43424.82187499998</v>
+        <v>56391.49687499999</v>
       </c>
       <c r="L14" s="32">
         <f>$D14*H14</f>
-        <v>95743.88437499997</v>
+        <v>124333.05937499997</v>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
@@ -22407,7 +22446,7 @@
       </c>
       <c r="D15" s="18">
         <f>q_1_4</f>
-        <v>29.880937500000005</v>
+        <v>33.158437500000005</v>
       </c>
       <c r="E15" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A15,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -22431,15 +22470,15 @@
       </c>
       <c r="J15" s="32">
         <f>$D15*F15</f>
-        <v>29880.937500000004</v>
+        <v>33158.43750000001</v>
       </c>
       <c r="K15" s="32">
         <f>$D15*G15</f>
-        <v>75598.77187500002</v>
+        <v>83890.84687500002</v>
       </c>
       <c r="L15" s="32">
         <f>$D15*H15</f>
-        <v>105479.70937500002</v>
+        <v>117049.28437500002</v>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
@@ -22465,7 +22504,7 @@
       </c>
       <c r="D16" s="18">
         <f>q_1_5</f>
-        <v>54.8</v>
+        <v>67.4</v>
       </c>
       <c r="E16" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A16,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -22485,19 +22524,19 @@
       </c>
       <c r="I16" s="32">
         <f>$D16*E16</f>
-        <v>65760.0</v>
+        <v>80880.0</v>
       </c>
       <c r="J16" s="32">
         <f>$D16*F16</f>
-        <v>10960.0</v>
+        <v>13480.000000000002</v>
       </c>
       <c r="K16" s="32">
         <f>$D16*G16</f>
-        <v>328.79999999999995</v>
+        <v>404.40000000000003</v>
       </c>
       <c r="L16" s="32">
         <f>$D16*H16</f>
-        <v>77048.8</v>
+        <v>94764.40000000001</v>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
@@ -22520,19 +22559,19 @@
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="36">
         <f>SUM(I12:I16)</f>
-        <v>65760.0</v>
+        <v>80880.0</v>
       </c>
       <c r="J17" s="36">
         <f>SUM(J12:J16)</f>
-        <v>312359.99999999994</v>
+        <v>384179.99999999994</v>
       </c>
       <c r="K17" s="36">
         <f>SUM(K12:K16)</f>
-        <v>125928.39375</v>
+        <v>148774.74375</v>
       </c>
       <c r="L17" s="36">
         <f>SUM(L12:L16)</f>
-        <v>504048.39374999993</v>
+        <v>613834.7437499999</v>
       </c>
       <c r="M17" s="34" t="n"/>
     </row>
@@ -22577,7 +22616,7 @@
       </c>
       <c r="D20" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="E20" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A20,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -22597,19 +22636,19 @@
       </c>
       <c r="I20" s="32">
         <f>$D20*E20</f>
-        <v>121245.00000000001</v>
+        <v>149122.50000000003</v>
       </c>
       <c r="J20" s="32">
         <f>$D20*F20</f>
-        <v>13700.000000000002</v>
+        <v>16850.000000000004</v>
       </c>
       <c r="K20" s="32">
         <f>$D20*G20</f>
-        <v>14111.000000000002</v>
+        <v>17355.500000000004</v>
       </c>
       <c r="L20" s="32">
         <f>$D20*H20</f>
-        <v>149056.0</v>
+        <v>183328.00000000003</v>
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
@@ -22799,7 +22838,7 @@
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>Béton armé dosé à 350 kg/m³ pour semelle filante 0,40 x 0,15</t>
+          <t>Béton armé dosé à 350 kg/m³ pour semelle filante 0,60 x 0,15</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -22809,7 +22848,7 @@
       </c>
       <c r="D24" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="E24" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A24,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -22829,19 +22868,19 @@
       </c>
       <c r="I24" s="32">
         <f>$D24*E24</f>
-        <v>268720.8</v>
+        <v>403081.2</v>
       </c>
       <c r="J24" s="32">
         <f>$D24*F24</f>
-        <v>26559.999999999996</v>
+        <v>39839.99999999999</v>
       </c>
       <c r="K24" s="32">
         <f>$D24*G24</f>
-        <v>27356.8</v>
+        <v>41035.2</v>
       </c>
       <c r="L24" s="32">
         <f>$D24*H24</f>
-        <v>322637.60000000003</v>
+        <v>483956.4000000001</v>
       </c>
       <c r="M24" s="12" t="inlineStr">
         <is>
@@ -23215,7 +23254,7 @@
       </c>
       <c r="D31" s="18">
         <f>q_2_12</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="E31" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A31,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -23235,19 +23274,19 @@
       </c>
       <c r="I31" s="32">
         <f>$D31*E31</f>
-        <v>121353.60824999999</v>
+        <v>137903.70825</v>
       </c>
       <c r="J31" s="32">
         <f>$D31*F31</f>
-        <v>13673.645999999999</v>
+        <v>15538.446</v>
       </c>
       <c r="K31" s="32">
         <f>$D31*G31</f>
-        <v>410.20938</v>
+        <v>466.15337999999997</v>
       </c>
       <c r="L31" s="32">
         <f>$D31*H31</f>
-        <v>135437.46362999998</v>
+        <v>153908.30763</v>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
@@ -23270,19 +23309,19 @@
       <c r="H32" s="34" t="n"/>
       <c r="I32" s="36">
         <f>SUM(I20:I31)</f>
-        <v>2810415.5128500005</v>
+        <v>2989203.5128500005</v>
       </c>
       <c r="J32" s="36">
         <f>SUM(J20:J31)</f>
-        <v>525414.182</v>
+        <v>543708.982</v>
       </c>
       <c r="K32" s="36">
         <f>SUM(K20:K31)</f>
-        <v>119860.42546000001</v>
+        <v>136839.26946</v>
       </c>
       <c r="L32" s="36">
         <f>SUM(L20:L31)</f>
-        <v>3455690.1203100006</v>
+        <v>3669751.7643100005</v>
       </c>
       <c r="M32" s="34" t="n"/>
     </row>
@@ -23317,7 +23356,7 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>Maçonnerie d'agglos 15 pleins en élévation, mortier dosé à 300 kg/m³ (y compris pignons)</t>
+          <t>Maçonnerie d'agglos 15 creux en élévation h = 6,00 m, mortier dosé à 300 kg/m³ (y compris pignons)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -23331,35 +23370,35 @@
       </c>
       <c r="E35" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A35,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
-        <v>7802.5</v>
+        <v>6314.0</v>
       </c>
       <c r="F35" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A35,'Sous-détails'!$B$5:$B$407,"Main-d'œuvre")</f>
-        <v>1500.0</v>
+        <v>1250.0</v>
       </c>
       <c r="G35" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A35,'Sous-détails'!$B$5:$B$407,"Matériel")</f>
-        <v>45.0</v>
+        <v>37.5</v>
       </c>
       <c r="H35" s="32">
         <f>E35+F35+G35</f>
-        <v>9347.5</v>
+        <v>7601.5</v>
       </c>
       <c r="I35" s="32">
         <f>$D35*E35</f>
-        <v>2917296.9201471154</v>
+        <v>2360757.802474705</v>
       </c>
       <c r="J35" s="32">
         <f>$D35*F35</f>
-        <v>560838.8824377665</v>
+        <v>467365.73536480544</v>
       </c>
       <c r="K35" s="32">
         <f>$D35*G35</f>
-        <v>16825.166473132995</v>
+        <v>14020.972060944163</v>
       </c>
       <c r="L35" s="32">
         <f>$D35*H35</f>
-        <v>3494960.969058015</v>
+        <v>2842144.509900455</v>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
@@ -23846,19 +23885,19 @@
       <c r="H44" s="34" t="n"/>
       <c r="I44" s="36">
         <f>SUM(I35:I43)</f>
-        <v>5261733.697071172</v>
+        <v>4705194.579398762</v>
       </c>
       <c r="J44" s="36">
         <f>SUM(J35:J43)</f>
-        <v>1132197.941987913</v>
+        <v>1038724.794914952</v>
       </c>
       <c r="K44" s="36">
         <f>SUM(K35:K43)</f>
-        <v>128441.95582187087</v>
+        <v>125637.76140968205</v>
       </c>
       <c r="L44" s="36">
         <f>SUM(L35:L43)</f>
-        <v>6522373.594880956</v>
+        <v>5869557.135723396</v>
       </c>
       <c r="M44" s="34" t="n"/>
     </row>
@@ -24469,7 +24508,7 @@
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Armatures HA10 FeE500 - dallage double nappe e = 20 cm + chaises</t>
+          <t>Armatures HA10 FeE500 - dallage nappe simple e = 20 cm + chaises</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -24479,7 +24518,7 @@
       </c>
       <c r="D59" s="18">
         <f>q_5_6</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="E59" s="32">
         <f>SUMIFS('Sous-détails'!$H$5:$H$407,'Sous-détails'!$A$5:$A$407,"Art. "&amp;$A59,'Sous-détails'!$B$5:$B$407,"Matériaux")</f>
@@ -24499,19 +24538,19 @@
       </c>
       <c r="I59" s="32">
         <f>$D59*E59</f>
-        <v>3615547.8888191245</v>
+        <v>1871204.6091256873</v>
       </c>
       <c r="J59" s="32">
         <f>$D59*F59</f>
-        <v>325725.03502874996</v>
+        <v>168576.99181312497</v>
       </c>
       <c r="K59" s="32">
         <f>$D59*G59</f>
-        <v>9771.751050862498</v>
+        <v>5057.309754393749</v>
       </c>
       <c r="L59" s="32">
         <f>$D59*H59</f>
-        <v>3951044.6748987366</v>
+        <v>2044838.910693206</v>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
@@ -24650,19 +24689,19 @@
       <c r="H62" s="34" t="n"/>
       <c r="I62" s="36">
         <f>SUM(I54:I61)</f>
-        <v>9370019.413819125</v>
+        <v>7625676.134125687</v>
       </c>
       <c r="J62" s="36">
         <f>SUM(J54:J61)</f>
-        <v>1078377.2766954168</v>
+        <v>921229.2334797917</v>
       </c>
       <c r="K62" s="36">
         <f>SUM(K54:K61)</f>
-        <v>909940.4433008626</v>
+        <v>905226.0020043938</v>
       </c>
       <c r="L62" s="36">
         <f>SUM(L54:L61)</f>
-        <v>11358337.133815404</v>
+        <v>9452131.369609874</v>
       </c>
       <c r="M62" s="34" t="n"/>
     </row>
@@ -25184,19 +25223,19 @@
       </c>
       <c r="I79" s="37">
         <f>SUMIFS(I5:I78,$M$5:$M$78,"NON")</f>
-        <v>21670975.65580921</v>
+        <v>19564001.258443363</v>
       </c>
       <c r="J79" s="37">
         <f>SUMIFS(J5:J78,$M$5:$M$78,"NON")</f>
-        <v>4310598.0976805035</v>
+        <v>4150091.7073919172</v>
       </c>
       <c r="K79" s="37">
         <f>SUMIFS(K5:K78,$M$5:$M$78,"NON")</f>
-        <v>1797002.3665219704</v>
+        <v>1829308.9248133127</v>
       </c>
       <c r="L79" s="37">
         <f>SUMIFS(L5:L78,$M$5:$M$78,"NON")</f>
-        <v>27778576.120011684</v>
+        <v>25543401.890648592</v>
       </c>
     </row>
     <row r="80">
@@ -25230,19 +25269,19 @@
       </c>
       <c r="I81" s="37">
         <f>I79+I80</f>
-        <v>30333279.104530834</v>
+        <v>28226304.707164988</v>
       </c>
       <c r="J81" s="37">
         <f>J79+J80</f>
-        <v>7120691.035935214</v>
+        <v>6960184.645646627</v>
       </c>
       <c r="K81" s="37">
         <f>K79+K80</f>
-        <v>2519208.1546696117</v>
+        <v>2551514.712960954</v>
       </c>
       <c r="L81" s="37">
         <f>L79+L80</f>
-        <v>39973178.29513566</v>
+        <v>37738004.06577257</v>
       </c>
     </row>
     <row r="82">
@@ -25253,15 +25292,15 @@
       </c>
       <c r="I82" s="39">
         <f>IF($L$79=0,0,I79/$L$79)</f>
-        <v>0.7801327023452955</v>
+        <v>0.7659121264347221</v>
       </c>
       <c r="J82" s="39">
         <f>IF($L$79=0,0,J79/$L$79)</f>
-        <v>0.15517707167773617</v>
+        <v>0.16247216111457968</v>
       </c>
       <c r="K82" s="39">
         <f>IF($L$79=0,0,K79/$L$79)</f>
-        <v>0.06469022597696827</v>
+        <v>0.0716157124506983</v>
       </c>
       <c r="L82" s="39">
         <f>IF($L$79=0,0,L79/$L$79)</f>
@@ -25511,7 +25550,7 @@
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>Fouilles en rigole 0,60 x 1,20 m en terrain latéritique</t>
+          <t>Fouilles en rigole 0,80 x 1,20 m en terrain latéritique</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -25521,7 +25560,7 @@
       </c>
       <c r="D12" s="18">
         <f>q_1_1</f>
-        <v>57.599999999999994</v>
+        <v>76.8</v>
       </c>
       <c r="E12" s="32">
         <f>ROUND('Déboursé sec'!H12*p_K/5,0)*5</f>
@@ -25529,7 +25568,7 @@
       </c>
       <c r="F12" s="32">
         <f>D12*E12</f>
-        <v>259487.99999999997</v>
+        <v>345984.0</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -25555,7 +25594,7 @@
       </c>
       <c r="D13" s="18">
         <f>q_1_2</f>
-        <v>8.16</v>
+        <v>4.079999999999999</v>
       </c>
       <c r="E13" s="32">
         <f>ROUND('Déboursé sec'!H13*p_K/5,0)*5</f>
@@ -25563,7 +25602,7 @@
       </c>
       <c r="F13" s="32">
         <f>D13*E13</f>
-        <v>36760.8</v>
+        <v>18380.399999999998</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -25589,7 +25628,7 @@
       </c>
       <c r="D14" s="18">
         <f>q_1_3</f>
-        <v>41.855249999999984</v>
+        <v>54.35324999999999</v>
       </c>
       <c r="E14" s="32">
         <f>ROUND('Déboursé sec'!H14*p_K/5,0)*5</f>
@@ -25597,7 +25636,7 @@
       </c>
       <c r="F14" s="32">
         <f>D14*E14</f>
-        <v>125565.74999999996</v>
+        <v>163059.74999999997</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -25623,7 +25662,7 @@
       </c>
       <c r="D15" s="18">
         <f>q_1_4</f>
-        <v>29.880937500000005</v>
+        <v>33.158437500000005</v>
       </c>
       <c r="E15" s="32">
         <f>ROUND('Déboursé sec'!H15*p_K/5,0)*5</f>
@@ -25631,7 +25670,7 @@
       </c>
       <c r="F15" s="32">
         <f>D15*E15</f>
-        <v>138498.1453125</v>
+        <v>153689.35781250003</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -25657,7 +25696,7 @@
       </c>
       <c r="D16" s="18">
         <f>q_1_5</f>
-        <v>54.8</v>
+        <v>67.4</v>
       </c>
       <c r="E16" s="32">
         <f>ROUND('Déboursé sec'!H16*p_K/5,0)*5</f>
@@ -25665,7 +25704,7 @@
       </c>
       <c r="F16" s="32">
         <f>D16*E16</f>
-        <v>101106.0</v>
+        <v>124353.00000000001</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -25685,7 +25724,7 @@
       <c r="E17" s="34" t="n"/>
       <c r="F17" s="36">
         <f>SUM(F12:F16)</f>
-        <v>661418.6953125</v>
+        <v>805466.5078125</v>
       </c>
       <c r="G17" s="34" t="n"/>
     </row>
@@ -25724,7 +25763,7 @@
       </c>
       <c r="D20" s="18">
         <f>q_2_1</f>
-        <v>2.74</v>
+        <v>3.3700000000000006</v>
       </c>
       <c r="E20" s="32">
         <f>ROUND('Déboursé sec'!H20*p_K/5,0)*5</f>
@@ -25732,7 +25771,7 @@
       </c>
       <c r="F20" s="32">
         <f>D20*E20</f>
-        <v>195636.00000000003</v>
+        <v>240618.00000000003</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -25850,7 +25889,7 @@
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>Béton armé dosé à 350 kg/m³ pour semelle filante 0,40 x 0,15</t>
+          <t>Béton armé dosé à 350 kg/m³ pour semelle filante 0,60 x 0,15</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -25860,7 +25899,7 @@
       </c>
       <c r="D24" s="18">
         <f>q_2_5</f>
-        <v>3.984</v>
+        <v>5.976</v>
       </c>
       <c r="E24" s="32">
         <f>ROUND('Déboursé sec'!H24*p_K/5,0)*5</f>
@@ -25868,7 +25907,7 @@
       </c>
       <c r="F24" s="32">
         <f>D24*E24</f>
-        <v>423459.36</v>
+        <v>635189.04</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -26098,7 +26137,7 @@
       </c>
       <c r="D31" s="18">
         <f>q_2_12</f>
-        <v>136.73646</v>
+        <v>155.38446</v>
       </c>
       <c r="E31" s="32">
         <f>ROUND('Déboursé sec'!H31*p_K/5,0)*5</f>
@@ -26106,7 +26145,7 @@
       </c>
       <c r="F31" s="32">
         <f>D31*E31</f>
-        <v>177757.398</v>
+        <v>201999.79799999998</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -26126,7 +26165,7 @@
       <c r="E32" s="34" t="n"/>
       <c r="F32" s="36">
         <f>SUM(F20:F31)</f>
-        <v>4536755.7334</v>
+        <v>4817709.8134</v>
       </c>
       <c r="G32" s="34" t="n"/>
     </row>
@@ -26155,7 +26194,7 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>Maçonnerie d'agglos 15 pleins en élévation, mortier dosé à 300 kg/m³ (y compris pignons)</t>
+          <t>Maçonnerie d'agglos 15 creux en élévation h = 6,00 m, mortier dosé à 300 kg/m³ (y compris pignons)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -26169,11 +26208,11 @@
       </c>
       <c r="E35" s="32">
         <f>ROUND('Déboursé sec'!H35*p_K/5,0)*5</f>
-        <v>12270.0</v>
+        <v>9975.0</v>
       </c>
       <c r="F35" s="32">
         <f>D35*E35</f>
-        <v>4587662.05834093</v>
+        <v>3729578.568211147</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -26465,7 +26504,7 @@
       <c r="E44" s="34" t="n"/>
       <c r="F44" s="36">
         <f>SUM(F35:F43)</f>
-        <v>8563924.253423713</v>
+        <v>7705840.76329393</v>
       </c>
       <c r="G44" s="34" t="n"/>
     </row>
@@ -26833,7 +26872,7 @@
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Armatures HA10 FeE500 - dallage double nappe e = 20 cm + chaises</t>
+          <t>Armatures HA10 FeE500 - dallage nappe simple e = 20 cm + chaises</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -26843,7 +26882,7 @@
       </c>
       <c r="D59" s="18">
         <f>q_5_6</f>
-        <v>4343.000467049999</v>
+        <v>2247.6932241749996</v>
       </c>
       <c r="E59" s="32">
         <f>ROUND('Déboursé sec'!H59*p_K/5,0)*5</f>
@@ -26851,7 +26890,7 @@
       </c>
       <c r="F59" s="32">
         <f>D59*E59</f>
-        <v>5189885.558124749</v>
+        <v>2685993.4028891246</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -26939,7 +26978,7 @@
       <c r="E62" s="34" t="n"/>
       <c r="F62" s="36">
         <f>SUM(F54:F61)</f>
-        <v>14912092.470624749</v>
+        <v>12408200.315389125</v>
       </c>
       <c r="G62" s="34" t="n"/>
     </row>
@@ -27282,7 +27321,7 @@
       </c>
       <c r="F81" s="32">
         <f>F17</f>
-        <v>661418.6953125</v>
+        <v>805466.5078125</v>
       </c>
     </row>
     <row r="82">
@@ -27298,7 +27337,7 @@
       </c>
       <c r="F82" s="32">
         <f>F32</f>
-        <v>4536755.7334</v>
+        <v>4817709.8134</v>
       </c>
     </row>
     <row r="83">
@@ -27314,7 +27353,7 @@
       </c>
       <c r="F83" s="32">
         <f>F44</f>
-        <v>8563924.253423713</v>
+        <v>7705840.76329393</v>
       </c>
     </row>
     <row r="84">
@@ -27346,7 +27385,7 @@
       </c>
       <c r="F85" s="32">
         <f>F62</f>
-        <v>14912092.470624749</v>
+        <v>12408200.315389125</v>
       </c>
     </row>
     <row r="86">
@@ -27357,7 +27396,7 @@
       </c>
       <c r="F86" s="37">
         <f>SUM(F80:F85)</f>
-        <v>36469963.295078956</v>
+        <v>33532989.542213544</v>
       </c>
     </row>
     <row r="87">
@@ -27372,7 +27411,7 @@
       </c>
       <c r="F87" s="32">
         <f>F86*p_TVA</f>
-        <v>6564593.393114212</v>
+        <v>6035938.117598438</v>
       </c>
     </row>
     <row r="88">
@@ -27383,7 +27422,7 @@
       </c>
       <c r="F88" s="37">
         <f>F86+F87</f>
-        <v>43034556.688193165</v>
+        <v>39568927.65981198</v>
       </c>
     </row>
     <row r="90">
@@ -27453,7 +27492,7 @@
       </c>
       <c r="F95" s="37">
         <f>F86+F93</f>
-        <v>52477206.225700706</v>
+        <v>49540232.472835295</v>
       </c>
     </row>
     <row r="96">
@@ -27468,7 +27507,7 @@
       </c>
       <c r="F96" s="32">
         <f>F95*p_TVA</f>
-        <v>9445897.120626127</v>
+        <v>8917241.845110353</v>
       </c>
     </row>
     <row r="97">
@@ -27479,7 +27518,7 @@
       </c>
       <c r="F97" s="37">
         <f>F95+F96</f>
-        <v>61923103.346326835</v>
+        <v>58457474.317945644</v>
       </c>
     </row>
     <row r="99">
@@ -27490,7 +27529,7 @@
       </c>
       <c r="F99" s="32">
         <f>F86/(p_L*p_B)</f>
-        <v>121566.54431692985</v>
+        <v>111776.63180737848</v>
       </c>
     </row>
     <row r="100">
@@ -27501,7 +27540,7 @@
       </c>
       <c r="F100" s="32">
         <f>F86-'Déboursé sec'!$L$79</f>
-        <v>8691387.175067272</v>
+        <v>7989587.651564952</v>
       </c>
     </row>
     <row r="102">
@@ -27546,7 +27585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27654,11 +27693,11 @@
       </c>
       <c r="D6" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A6,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>643.7910005373401</v>
+        <v>652.1471487715032</v>
       </c>
       <c r="E6" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A6)</f>
-        <v>764.2022005373401</v>
+        <v>772.5583487715032</v>
       </c>
       <c r="F6" s="32">
         <f>px_ciment</f>
@@ -27666,15 +27705,15 @@
       </c>
       <c r="G6" s="32">
         <f>D6*F6</f>
-        <v>3733987.8031165726</v>
+        <v>3782453.4628747185</v>
       </c>
       <c r="H6" s="32">
         <f>E6*F6</f>
-        <v>4432372.763116573</v>
+        <v>4480838.422874719</v>
       </c>
       <c r="I6" s="10" t="str">
         <f>ROUND(D6*50/1000,1)&amp;" t (gros œuvre)"</f>
-        <v>32.2 t (gros œuvre)</v>
+        <v>32.6 t (gros œuvre)</v>
       </c>
     </row>
     <row r="7">
@@ -27695,11 +27734,11 @@
       </c>
       <c r="D7" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A7,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>51.41455243905583</v>
+        <v>50.72498949759661</v>
       </c>
       <c r="E7" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A7)</f>
-        <v>74.57055243905583</v>
+        <v>73.88098949759662</v>
       </c>
       <c r="F7" s="32">
         <f>px_sable</f>
@@ -27707,11 +27746,11 @@
       </c>
       <c r="G7" s="32">
         <f>D7*F7</f>
-        <v>616974.62926867</v>
+        <v>608699.8739711593</v>
       </c>
       <c r="H7" s="32">
         <f>E7*F7</f>
-        <v>894846.62926867</v>
+        <v>886571.8739711593</v>
       </c>
       <c r="I7" s="10" t="n"/>
     </row>
@@ -27733,11 +27772,11 @@
       </c>
       <c r="D8" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A8,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>71.04585749278985</v>
+        <v>73.27455749278985</v>
       </c>
       <c r="E8" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A8)</f>
-        <v>71.04585749278985</v>
+        <v>73.27455749278985</v>
       </c>
       <c r="F8" s="32">
         <f>px_gravier</f>
@@ -27745,11 +27784,11 @@
       </c>
       <c r="G8" s="32">
         <f>D8*F8</f>
-        <v>1776146.4373197462</v>
+        <v>1831863.9373197462</v>
       </c>
       <c r="H8" s="32">
         <f>E8*F8</f>
-        <v>1776146.4373197462</v>
+        <v>1831863.9373197462</v>
       </c>
       <c r="I8" s="10" t="n"/>
     </row>
@@ -27771,11 +27810,11 @@
       </c>
       <c r="D9" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A9,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>32.94679823416311</v>
+        <v>33.47119823416311</v>
       </c>
       <c r="E9" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A9)</f>
-        <v>42.20919823416311</v>
+        <v>42.73359823416311</v>
       </c>
       <c r="F9" s="32">
         <f>px_eau</f>
@@ -27783,11 +27822,11 @@
       </c>
       <c r="G9" s="32">
         <f>D9*F9</f>
-        <v>32946.798234163114</v>
+        <v>33471.19823416311</v>
       </c>
       <c r="H9" s="32">
         <f>E9*F9</f>
-        <v>42209.19823416311</v>
+        <v>42733.59823416311</v>
       </c>
       <c r="I9" s="10" t="n"/>
     </row>
@@ -27809,11 +27848,11 @@
       </c>
       <c r="D10" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A10,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>5865.858971330457</v>
+        <v>958.5187500000001</v>
       </c>
       <c r="E10" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A10)</f>
-        <v>5865.858971330457</v>
+        <v>958.5187500000001</v>
       </c>
       <c r="F10" s="32">
         <f>px_agglo</f>
@@ -27821,762 +27860,762 @@
       </c>
       <c r="G10" s="32">
         <f>D10*F10</f>
-        <v>2932929.4856652287</v>
+        <v>479259.37500000006</v>
       </c>
       <c r="H10" s="32">
         <f>E10*F10</f>
-        <v>2932929.4856652287</v>
+        <v>479259.37500000006</v>
       </c>
       <c r="I10" s="10" t="str">
         <f>ROUNDUP(D10,0)&amp;" agglos (GO)"</f>
-        <v>5866 agglos (GO)</v>
+        <v>959 agglos (GO)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>ha6</t>
+          <t>agglo_cr</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Acier HA6 FeE500 (barre 12 m = 2,66 kg à 2 300)</t>
+          <t>Agglo 15 creux 40x20x15 rendu chantier</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D11" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A11,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>453.2839744861848</v>
+        <v>4907.340221330457</v>
       </c>
       <c r="E11" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A11)</f>
-        <v>453.2839744861848</v>
+        <v>4907.340221330457</v>
       </c>
       <c r="F11" s="32">
+        <f>px_agglo_cr</f>
+        <v>400.0</v>
+      </c>
+      <c r="G11" s="32">
+        <f>D11*F11</f>
+        <v>1962936.0885321829</v>
+      </c>
+      <c r="H11" s="32">
+        <f>E11*F11</f>
+        <v>1962936.0885321829</v>
+      </c>
+      <c r="I11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>ha6</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Acier HA6 FeE500 (barre 12 m = 2,66 kg à 2 300)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D12" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A12,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>471.9319744861848</v>
+      </c>
+      <c r="E12" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A12)</f>
+        <v>471.9319744861848</v>
+      </c>
+      <c r="F12" s="32">
         <f>px_ha6</f>
         <v>865.0</v>
       </c>
-      <c r="G11" s="32">
-        <f>D11*F11</f>
-        <v>392090.63793054986</v>
-      </c>
-      <c r="H11" s="32">
-        <f>E11*F11</f>
-        <v>392090.63793054986</v>
-      </c>
-      <c r="I11" s="10" t="str">
-        <f>ROUNDUP(D11/(12*p_KG6),0)&amp;" barres de 12 m (GO)"</f>
-        <v>171 barres de 12 m (GO)</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="G12" s="32">
+        <f>D12*F12</f>
+        <v>408221.1579305499</v>
+      </c>
+      <c r="H12" s="32">
+        <f>E12*F12</f>
+        <v>408221.1579305499</v>
+      </c>
+      <c r="I12" s="10" t="str">
+        <f>ROUNDUP(D12/(12*p_KG6),0)&amp;" barres de 12 m (GO)"</f>
+        <v>178 barres de 12 m (GO)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>ha10</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Acier HA10 FeE500 (barre 12 m = 7,40 kg à 6 000)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D12" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A12,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>5991.482483387106</v>
-      </c>
-      <c r="E12" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A12)</f>
-        <v>5991.482483387106</v>
-      </c>
-      <c r="F12" s="32">
+      <c r="D13" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A13,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>3896.175240512107</v>
+      </c>
+      <c r="E13" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A13)</f>
+        <v>3896.175240512107</v>
+      </c>
+      <c r="F13" s="32">
         <f>px_ha10</f>
         <v>810.0</v>
       </c>
-      <c r="G12" s="32">
-        <f>D12*F12</f>
-        <v>4853100.811543556</v>
-      </c>
-      <c r="H12" s="32">
-        <f>E12*F12</f>
-        <v>4853100.811543556</v>
-      </c>
-      <c r="I12" s="10" t="str">
-        <f>ROUNDUP(D12/(12*p_KG10),0)&amp;" barres de 12 m (GO)"</f>
-        <v>810 barres de 12 m (GO)</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="G13" s="32">
+        <f>D13*F13</f>
+        <v>3155901.944814807</v>
+      </c>
+      <c r="H13" s="32">
+        <f>E13*F13</f>
+        <v>3155901.944814807</v>
+      </c>
+      <c r="I13" s="10" t="str">
+        <f>ROUNDUP(D13/(12*p_KG10),0)&amp;" barres de 12 m (GO)"</f>
+        <v>527 barres de 12 m (GO)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>ha12</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Acier HA12 FeE500 (barre 12 m = 10,66 kg à 8 500)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D13" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A13,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D14" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A14,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>288.48456000000004</v>
       </c>
-      <c r="E13" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A13)</f>
+      <c r="E14" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A14)</f>
         <v>288.48456000000004</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F14" s="32">
         <f>px_ha12</f>
         <v>800.0</v>
       </c>
-      <c r="G13" s="32">
-        <f>D13*F13</f>
+      <c r="G14" s="32">
+        <f>D14*F14</f>
         <v>230787.64800000004</v>
       </c>
-      <c r="H13" s="32">
-        <f>E13*F13</f>
+      <c r="H14" s="32">
+        <f>E14*F14</f>
         <v>230787.64800000004</v>
       </c>
-      <c r="I13" s="10" t="str">
-        <f>ROUNDUP(D13/(12*p_KG12),0)&amp;" barres de 12 m (GO)"</f>
+      <c r="I14" s="10" t="str">
+        <f>ROUNDUP(D14/(12*p_KG12),0)&amp;" barres de 12 m (GO)"</f>
         <v>28 barres de 12 m (GO)</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>fil</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Fil recuit</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D14" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A14,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>100.99876526809936</v>
-      </c>
-      <c r="E14" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A14)</f>
-        <v>100.99876526809936</v>
-      </c>
-      <c r="F14" s="32">
+      <c r="D15" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A15,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>69.84887662497437</v>
+      </c>
+      <c r="E15" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A15)</f>
+        <v>69.84887662497437</v>
+      </c>
+      <c r="F15" s="32">
         <f>px_fil</f>
         <v>1500.0</v>
       </c>
-      <c r="G14" s="32">
-        <f>D14*F14</f>
-        <v>151498.14790214904</v>
-      </c>
-      <c r="H14" s="32">
-        <f>E14*F14</f>
-        <v>151498.14790214904</v>
-      </c>
-      <c r="I14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="G15" s="32">
+        <f>D15*F15</f>
+        <v>104773.31493746155</v>
+      </c>
+      <c r="H15" s="32">
+        <f>E15*F15</f>
+        <v>104773.31493746155</v>
+      </c>
+      <c r="I15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>bois</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Bois de coffrage (amorti 3 emplois)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A15,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D16" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A16,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>248.75982341631132</v>
       </c>
-      <c r="E15" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A15)</f>
+      <c r="E16" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A16)</f>
         <v>248.75982341631132</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F16" s="32">
         <f>px_bois</f>
         <v>1800.0</v>
       </c>
-      <c r="G15" s="32">
-        <f>D15*F15</f>
+      <c r="G16" s="32">
+        <f>D16*F16</f>
         <v>447767.68214936036</v>
       </c>
-      <c r="H15" s="32">
-        <f>E15*F15</f>
+      <c r="H16" s="32">
+        <f>E16*F16</f>
         <v>447767.68214936036</v>
       </c>
-      <c r="I15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="I16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>pointes</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Pointes</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D16" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A16,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D17" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A17,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>36.2939735124467</v>
       </c>
-      <c r="E16" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A16)</f>
+      <c r="E17" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A17)</f>
         <v>36.2939735124467</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F17" s="32">
         <f>px_pointes</f>
         <v>1500.0</v>
       </c>
-      <c r="G16" s="32">
-        <f>D16*F16</f>
+      <c r="G17" s="32">
+        <f>D17*F17</f>
         <v>54440.960268670045</v>
       </c>
-      <c r="H16" s="32">
-        <f>E16*F16</f>
+      <c r="H17" s="32">
+        <f>E17*F17</f>
         <v>54440.960268670045</v>
       </c>
-      <c r="I16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>huile</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Huile de décoffrage</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D17" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A17,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D18" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A18,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>24.195982341631133</v>
       </c>
-      <c r="E17" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A17)</f>
+      <c r="E18" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A18)</f>
         <v>24.195982341631133</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F18" s="32">
         <f>px_huile</f>
         <v>1000.0</v>
       </c>
-      <c r="G17" s="32">
-        <f>D17*F17</f>
+      <c r="G18" s="32">
+        <f>D18*F18</f>
         <v>24195.982341631134</v>
       </c>
-      <c r="H17" s="32">
-        <f>E17*F17</f>
+      <c r="H18" s="32">
+        <f>E18*F18</f>
         <v>24195.982341631134</v>
       </c>
-      <c r="I17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="I18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>hydro</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Hydrofuge de masse</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D18" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A18,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D19" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A19,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>5.47725</v>
       </c>
-      <c r="E18" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A18)</f>
+      <c r="E19" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A19)</f>
         <v>5.47725</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F19" s="32">
         <f>px_hydro</f>
         <v>2000.0</v>
       </c>
-      <c r="G18" s="32">
-        <f>D18*F18</f>
+      <c r="G19" s="32">
+        <f>D19*F19</f>
         <v>10954.5</v>
       </c>
-      <c r="H18" s="32">
-        <f>E18*F18</f>
+      <c r="H19" s="32">
+        <f>E19*F19</f>
         <v>10954.5</v>
       </c>
-      <c r="I18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="I19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>termite</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Produit anti-termites (dilué)</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D19" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A19,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>348.8225</v>
-      </c>
-      <c r="E19" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A19)</f>
-        <v>348.8225</v>
-      </c>
-      <c r="F19" s="32">
+      <c r="D20" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A20,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>361.4225</v>
+      </c>
+      <c r="E20" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A20)</f>
+        <v>361.4225</v>
+      </c>
+      <c r="F20" s="32">
         <f>px_termite</f>
         <v>1200.0</v>
       </c>
-      <c r="G19" s="32">
-        <f>D19*F19</f>
-        <v>418587.0</v>
-      </c>
-      <c r="H19" s="32">
-        <f>E19*F19</f>
-        <v>418587.0</v>
-      </c>
-      <c r="I19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="G20" s="32">
+        <f>D20*F20</f>
+        <v>433707.0</v>
+      </c>
+      <c r="H20" s="32">
+        <f>E20*F20</f>
+        <v>433707.0</v>
+      </c>
+      <c r="I20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>laterite</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Latérite d'emprunt rendue chantier</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="D20" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A20,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D21" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A21,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>152.8917</v>
       </c>
-      <c r="E20" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A20)</f>
+      <c r="E21" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A21)</f>
         <v>152.8917</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F21" s="32">
         <f>px_laterite</f>
         <v>6000.0</v>
       </c>
-      <c r="G20" s="32">
-        <f>D20*F20</f>
+      <c r="G21" s="32">
+        <f>D21*F21</f>
         <v>917350.2</v>
       </c>
-      <c r="H20" s="32">
-        <f>E20*F20</f>
+      <c r="H21" s="32">
+        <f>E21*F21</f>
         <v>917350.2</v>
       </c>
-      <c r="I20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>polyane</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Film polyane 150 µ</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D21" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A21,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D22" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A22,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>323.42475</v>
       </c>
-      <c r="E21" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A21)</f>
+      <c r="E22" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A22)</f>
         <v>323.42475</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F22" s="32">
         <f>px_polyane</f>
         <v>400.0</v>
       </c>
-      <c r="G21" s="32">
-        <f>D21*F21</f>
+      <c r="G22" s="32">
+        <f>D22*F22</f>
         <v>129369.90000000001</v>
       </c>
-      <c r="H21" s="32">
-        <f>E21*F21</f>
+      <c r="H22" s="32">
+        <f>E22*F22</f>
         <v>129369.90000000001</v>
       </c>
-      <c r="I21" s="10" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="I22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>joint</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Fond de joint + mastic / joint périphérique</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="D22" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A22,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D23" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A23,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>158.5</v>
       </c>
-      <c r="E22" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A22)</f>
+      <c r="E23" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A23)</f>
         <v>158.5</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F23" s="32">
         <f>px_joint</f>
         <v>800.0</v>
       </c>
-      <c r="G22" s="32">
-        <f>D22*F22</f>
+      <c r="G23" s="32">
+        <f>D23*F23</f>
         <v>126800.0</v>
       </c>
-      <c r="H22" s="32">
-        <f>E22*F22</f>
+      <c r="H23" s="32">
+        <f>E23*F23</f>
         <v>126800.0</v>
       </c>
-      <c r="I22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>ipe</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Profilé IPE 220 (S235)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D23" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A23,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D24" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A24,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>2833.53</v>
       </c>
-      <c r="E23" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A23)</f>
+      <c r="E24" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A24)</f>
         <v>2833.53</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F24" s="32">
         <f>px_ipe</f>
         <v>950.0</v>
       </c>
-      <c r="G23" s="32">
-        <f>D23*F23</f>
+      <c r="G24" s="32">
+        <f>D24*F24</f>
         <v>2691853.5</v>
       </c>
-      <c r="H23" s="32">
-        <f>E23*F23</f>
+      <c r="H24" s="32">
+        <f>E24*F24</f>
         <v>2691853.5</v>
       </c>
-      <c r="I23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="I24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>corniere</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Cornière 50x50x5 (S235)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D24" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A24,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D25" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A25,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>520.8387164328776</v>
       </c>
-      <c r="E24" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A24)</f>
+      <c r="E25" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A25)</f>
         <v>520.8387164328776</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F25" s="32">
         <f>px_corniere</f>
         <v>900.0</v>
       </c>
-      <c r="G24" s="32">
-        <f>D24*F24</f>
+      <c r="G25" s="32">
+        <f>D25*F25</f>
         <v>468754.8447895899</v>
       </c>
-      <c r="H24" s="32">
-        <f>E24*F24</f>
+      <c r="H25" s="32">
+        <f>E25*F25</f>
         <v>468754.8447895899</v>
       </c>
-      <c r="I24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="I25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>tole</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Tôle pour platines et goussets ép. 15 mm</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D25" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A25,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D26" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A26,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>267.75</v>
       </c>
-      <c r="E25" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A25)</f>
+      <c r="E26" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A26)</f>
         <v>267.75</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F26" s="32">
         <f>px_tole</f>
         <v>900.0</v>
       </c>
-      <c r="G25" s="32">
-        <f>D25*F25</f>
+      <c r="G26" s="32">
+        <f>D26*F26</f>
         <v>240975.0</v>
       </c>
-      <c r="H25" s="32">
-        <f>E25*F25</f>
+      <c r="H26" s="32">
+        <f>E26*F26</f>
         <v>240975.0</v>
       </c>
-      <c r="I25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>tige</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Tige d'ancrage M20 L = 600 coudée + 2 écrous + rondelle</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D26" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A26,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D27" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A27,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>68.0</v>
       </c>
-      <c r="E26" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A26)</f>
+      <c r="E27" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A27)</f>
         <v>68.0</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F27" s="32">
         <f>px_tige</f>
         <v>6000.0</v>
       </c>
-      <c r="G26" s="32">
-        <f>D26*F26</f>
+      <c r="G27" s="32">
+        <f>D27*F27</f>
         <v>408000.0</v>
       </c>
-      <c r="H26" s="32">
-        <f>E26*F26</f>
+      <c r="H27" s="32">
+        <f>E27*F27</f>
         <v>408000.0</v>
       </c>
-      <c r="I26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="I27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>grout</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Mortier de calage sans retrait (sac 25 kg)</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>sac</t>
         </is>
       </c>
-      <c r="D27" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A27,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D28" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A28,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>8.5</v>
       </c>
-      <c r="E27" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A27)</f>
+      <c r="E28" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A28)</f>
         <v>8.5</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F28" s="32">
         <f>px_grout</f>
         <v>9000.0</v>
       </c>
-      <c r="G27" s="32">
-        <f>D27*F27</f>
+      <c r="G28" s="32">
+        <f>D28*F28</f>
         <v>76500.0</v>
       </c>
-      <c r="H27" s="32">
-        <f>E27*F27</f>
+      <c r="H28" s="32">
+        <f>E28*F28</f>
         <v>76500.0</v>
       </c>
-      <c r="I27" s="10" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="I28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>peint</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Peinture antirouille + finition (2 couches)</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D28" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A28,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D29" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A29,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>3449.6368727932168</v>
       </c>
-      <c r="E28" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A28)</f>
+      <c r="E29" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A29)</f>
         <v>3449.6368727932168</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F29" s="32">
         <f>px_peint</f>
         <v>100.0</v>
       </c>
-      <c r="G28" s="32">
-        <f>D28*F28</f>
-        <v>344963.68727932166</v>
-      </c>
-      <c r="H28" s="32">
-        <f>E28*F28</f>
-        <v>344963.68727932166</v>
-      </c>
-      <c r="I28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>acier_ch</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Profilés charpente de toiture + peinture</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D29" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A29,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E29" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A29)</f>
-        <v>2864.4</v>
-      </c>
-      <c r="F29" s="32">
-        <f>px_acier_ch</f>
-        <v>950.0</v>
-      </c>
       <c r="G29" s="32">
         <f>D29*F29</f>
-        <v>0.0</v>
+        <v>344963.68727932166</v>
       </c>
       <c r="H29" s="32">
         <f>E29*F29</f>
-        <v>2721180.0</v>
+        <v>344963.68727932166</v>
       </c>
       <c r="I29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>bac</t>
+          <t>acier_ch</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Tôle bac 5 ondes (alu 6/10 ou acier prélaqué) + fixations</t>
+          <t>Profilés charpente de toiture + peinture</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D30" s="18">
@@ -28585,11 +28624,11 @@
       </c>
       <c r="E30" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A30)</f>
-        <v>381.85313082702794</v>
+        <v>2864.4</v>
       </c>
       <c r="F30" s="32">
-        <f>px_bac</f>
-        <v>4500.0</v>
+        <f>px_acier_ch</f>
+        <v>950.0</v>
       </c>
       <c r="G30" s="32">
         <f>D30*F30</f>
@@ -28597,24 +28636,24 @@
       </c>
       <c r="H30" s="32">
         <f>E30*F30</f>
-        <v>1718339.0887216257</v>
+        <v>2721180.0</v>
       </c>
       <c r="I30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>zpanne</t>
+          <t>bac</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Panne Z 120 x 2 galvanisée + échantignoles + boulons</t>
+          <t>Tôle bac 5 ondes (alu 6/10 ou acier prélaqué) + fixations</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D31" s="18">
@@ -28623,11 +28662,11 @@
       </c>
       <c r="E31" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A31)</f>
-        <v>1523.3400000000001</v>
+        <v>381.85313082702794</v>
       </c>
       <c r="F31" s="32">
-        <f>px_zpanne</f>
-        <v>1000.0</v>
+        <f>px_bac</f>
+        <v>4500.0</v>
       </c>
       <c r="G31" s="32">
         <f>D31*F31</f>
@@ -28635,24 +28674,24 @@
       </c>
       <c r="H31" s="32">
         <f>E31*F31</f>
-        <v>1523340.0000000002</v>
+        <v>1718339.0887216257</v>
       </c>
       <c r="I31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>faitiere</t>
+          <t>zpanne</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Faîtière aluminium</t>
+          <t>Panne Z 120 x 2 galvanisée + échantignoles + boulons</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D32" s="18">
@@ -28661,11 +28700,11 @@
       </c>
       <c r="E32" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A32)</f>
-        <v>32.550000000000004</v>
+        <v>1523.3400000000001</v>
       </c>
       <c r="F32" s="32">
-        <f>px_faitiere</f>
-        <v>3500.0</v>
+        <f>px_zpanne</f>
+        <v>1000.0</v>
       </c>
       <c r="G32" s="32">
         <f>D32*F32</f>
@@ -28673,57 +28712,57 @@
       </c>
       <c r="H32" s="32">
         <f>E32*F32</f>
-        <v>113925.00000000001</v>
+        <v>1523340.0000000002</v>
       </c>
       <c r="I32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>ff_install</t>
+          <t>faitiere</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Magasin, clôture provisoire, panneau de chantier</t>
+          <t>Faîtière aluminium</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D33" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A33,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E33" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A33)</f>
-        <v>1.0</v>
+        <v>32.550000000000004</v>
       </c>
       <c r="F33" s="32">
-        <f>px_ff_install</f>
-        <v>300000.0</v>
+        <f>px_faitiere</f>
+        <v>3500.0</v>
       </c>
       <c r="G33" s="32">
         <f>D33*F33</f>
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H33" s="32">
         <f>E33*F33</f>
-        <v>300000.0</v>
+        <v>113925.00000000001</v>
       </c>
       <c r="I33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>ff_implant</t>
+          <t>ff_install</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Bois de chaises, cordeau, peinture</t>
+          <t>Magasin, clôture provisoire, panneau de chantier</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -28740,28 +28779,28 @@
         <v>1.0</v>
       </c>
       <c r="F34" s="32">
-        <f>px_ff_implant</f>
-        <v>40000.0</v>
+        <f>px_ff_install</f>
+        <v>300000.0</v>
       </c>
       <c r="G34" s="32">
         <f>D34*F34</f>
-        <v>40000.0</v>
+        <v>300000.0</v>
       </c>
       <c r="H34" s="32">
         <f>E34*F34</f>
-        <v>40000.0</v>
+        <v>300000.0</v>
       </c>
       <c r="I34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>ff_essais</t>
+          <t>ff_implant</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Essais labo (Proctor, densités in situ, écrasement béton)</t>
+          <t>Bois de chaises, cordeau, peinture</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -28778,28 +28817,28 @@
         <v>1.0</v>
       </c>
       <c r="F35" s="32">
-        <f>px_ff_essais</f>
-        <v>250000.0</v>
+        <f>px_ff_implant</f>
+        <v>40000.0</v>
       </c>
       <c r="G35" s="32">
         <f>D35*F35</f>
-        <v>250000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="H35" s="32">
         <f>E35*F35</f>
-        <v>250000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="I35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>ff_portail</t>
+          <t>ff_essais</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Portail : tubes, tôle 15/10, rail, roulettes, peinture</t>
+          <t>Essais labo (Proctor, densités in situ, écrasement béton)</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -28809,678 +28848,678 @@
       </c>
       <c r="D36" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A36,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E36" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A36)</f>
         <v>1.0</v>
       </c>
       <c r="F36" s="32">
+        <f>px_ff_essais</f>
+        <v>250000.0</v>
+      </c>
+      <c r="G36" s="32">
+        <f>D36*F36</f>
+        <v>250000.0</v>
+      </c>
+      <c r="H36" s="32">
+        <f>E36*F36</f>
+        <v>250000.0</v>
+      </c>
+      <c r="I36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>ff_portail</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Portail : tubes, tôle 15/10, rail, roulettes, peinture</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D37" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A37,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A37)</f>
+        <v>1.0</v>
+      </c>
+      <c r="F37" s="32">
         <f>px_ff_portail</f>
         <v>1600000.0</v>
       </c>
-      <c r="G36" s="32">
-        <f>D36*F36</f>
+      <c r="G37" s="32">
+        <f>D37*F37</f>
         <v>0.0</v>
       </c>
-      <c r="H36" s="32">
-        <f>E36*F36</f>
+      <c r="H37" s="32">
+        <f>E37*F37</f>
         <v>1600000.0</v>
       </c>
-      <c r="I36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="I37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>MAIN-D'ŒUVRE</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>mo_macon</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Maçon</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>h.j</t>
         </is>
       </c>
-      <c r="D38" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A38,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>62.504138434906935</v>
-      </c>
-      <c r="E38" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A38)</f>
-        <v>139.6908051015736</v>
-      </c>
-      <c r="F38" s="32">
+      <c r="D39" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A39,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>56.68334529670953</v>
+      </c>
+      <c r="E39" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A39)</f>
+        <v>133.87001196337621</v>
+      </c>
+      <c r="F39" s="32">
         <f>px_mo_macon</f>
         <v>10000.0</v>
       </c>
-      <c r="G38" s="32">
-        <f>D38*F38</f>
-        <v>625041.3843490693</v>
-      </c>
-      <c r="H38" s="32">
-        <f>E38*F38</f>
-        <v>1396908.051015736</v>
-      </c>
-      <c r="I38" s="10" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="G39" s="32">
+        <f>D39*F39</f>
+        <v>566833.4529670953</v>
+      </c>
+      <c r="H39" s="32">
+        <f>E39*F39</f>
+        <v>1338700.1196337622</v>
+      </c>
+      <c r="I39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>mo_ferr</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Ferrailleur</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>h.j</t>
         </is>
       </c>
-      <c r="D39" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A39,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>37.65000600740528</v>
-      </c>
-      <c r="E39" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A39)</f>
-        <v>37.65000600740528</v>
-      </c>
-      <c r="F39" s="32">
+      <c r="D40" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A40,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>27.297789793030276</v>
+      </c>
+      <c r="E40" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A40)</f>
+        <v>27.297789793030276</v>
+      </c>
+      <c r="F40" s="32">
         <f>px_mo_ferr</f>
         <v>10000.0</v>
       </c>
-      <c r="G39" s="32">
-        <f>D39*F39</f>
-        <v>376500.06007405283</v>
-      </c>
-      <c r="H39" s="32">
-        <f>E39*F39</f>
-        <v>376500.06007405283</v>
-      </c>
-      <c r="I39" s="10" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="G40" s="32">
+        <f>D40*F40</f>
+        <v>272977.8979303028</v>
+      </c>
+      <c r="H40" s="32">
+        <f>E40*F40</f>
+        <v>272977.8979303028</v>
+      </c>
+      <c r="I40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>mo_coff</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Coffreur</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>h.j</t>
         </is>
       </c>
-      <c r="D40" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A40,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D41" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A41,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>30.244977927038917</v>
       </c>
-      <c r="E40" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A40)</f>
+      <c r="E41" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A41)</f>
         <v>30.244977927038917</v>
       </c>
-      <c r="F40" s="32">
+      <c r="F41" s="32">
         <f>px_mo_coff</f>
         <v>10000.0</v>
       </c>
-      <c r="G40" s="32">
-        <f>D40*F40</f>
+      <c r="G41" s="32">
+        <f>D41*F41</f>
         <v>302449.7792703892</v>
       </c>
-      <c r="H40" s="32">
-        <f>E40*F40</f>
+      <c r="H41" s="32">
+        <f>E41*F41</f>
         <v>302449.7792703892</v>
       </c>
-      <c r="I40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>mo_soud</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Soudeur / couvreur</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>h.j</t>
         </is>
       </c>
-      <c r="D41" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A41,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D42" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A42,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>45.87828121322028</v>
       </c>
-      <c r="E41" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A41)</f>
+      <c r="E42" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A42)</f>
         <v>126.2123614592891</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F42" s="32">
         <f>px_mo_soud</f>
         <v>15000.0</v>
       </c>
-      <c r="G41" s="32">
-        <f>D41*F41</f>
+      <c r="G42" s="32">
+        <f>D42*F42</f>
         <v>688174.2181983043</v>
       </c>
-      <c r="H41" s="32">
-        <f>E41*F41</f>
+      <c r="H42" s="32">
+        <f>E42*F42</f>
         <v>1893185.4218893365</v>
       </c>
-      <c r="I41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="I42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>mo_tech</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Technicien</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>h.j</t>
         </is>
       </c>
-      <c r="D42" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A42,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D43" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A43,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>2.0</v>
       </c>
-      <c r="E42" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A42)</f>
+      <c r="E43" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A43)</f>
         <v>2.0</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F43" s="32">
         <f>px_mo_tech</f>
         <v>15000.0</v>
       </c>
-      <c r="G42" s="32">
-        <f>D42*F42</f>
+      <c r="G43" s="32">
+        <f>D43*F43</f>
         <v>30000.0</v>
       </c>
-      <c r="H42" s="32">
-        <f>E42*F42</f>
+      <c r="H43" s="32">
+        <f>E43*F43</f>
         <v>30000.0</v>
       </c>
-      <c r="I42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="I43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>mo_man</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Manœuvre</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>h.j</t>
         </is>
       </c>
-      <c r="D43" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A43,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>457.6865311577376</v>
-      </c>
-      <c r="E43" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A43)</f>
-        <v>624.3295447371397</v>
-      </c>
-      <c r="F43" s="32">
+      <c r="D44" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A44,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>457.9312718051651</v>
+      </c>
+      <c r="E44" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A44)</f>
+        <v>624.5742853845674</v>
+      </c>
+      <c r="F44" s="32">
         <f>px_mo_man</f>
         <v>5000.0</v>
       </c>
-      <c r="G43" s="32">
-        <f>D43*F43</f>
-        <v>2288432.655788688</v>
-      </c>
-      <c r="H43" s="32">
-        <f>E43*F43</f>
-        <v>3121647.7236856986</v>
-      </c>
-      <c r="I43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="G44" s="32">
+        <f>D44*F44</f>
+        <v>2289656.3590258257</v>
+      </c>
+      <c r="H44" s="32">
+        <f>E44*F44</f>
+        <v>3122871.426922837</v>
+      </c>
+      <c r="I44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>MATÉRIEL</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>mt_bet</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Bétonnière 350 L (location)</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D45" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A45,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>12.314912939055837</v>
-      </c>
-      <c r="E45" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A45)</f>
-        <v>12.314912939055837</v>
-      </c>
-      <c r="F45" s="32">
+      <c r="D46" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A46,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>12.725662939055837</v>
+      </c>
+      <c r="E46" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A46)</f>
+        <v>12.725662939055837</v>
+      </c>
+      <c r="F46" s="32">
         <f>px_mt_bet</f>
         <v>25000.0</v>
       </c>
-      <c r="G45" s="32">
-        <f>D45*F45</f>
-        <v>307872.8234763959</v>
-      </c>
-      <c r="H45" s="32">
-        <f>E45*F45</f>
-        <v>307872.8234763959</v>
-      </c>
-      <c r="I45" s="10" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="G46" s="32">
+        <f>D46*F46</f>
+        <v>318141.5734763959</v>
+      </c>
+      <c r="H46" s="32">
+        <f>E46*F46</f>
+        <v>318141.5734763959</v>
+      </c>
+      <c r="I46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>mt_vib</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Vibreur (location)</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D46" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A46,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>12.314912939055837</v>
-      </c>
-      <c r="E46" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A46)</f>
-        <v>12.314912939055837</v>
-      </c>
-      <c r="F46" s="32">
+      <c r="D47" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A47,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>12.725662939055837</v>
+      </c>
+      <c r="E47" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A47)</f>
+        <v>12.725662939055837</v>
+      </c>
+      <c r="F47" s="32">
         <f>px_mt_vib</f>
         <v>15000.0</v>
       </c>
-      <c r="G46" s="32">
-        <f>D46*F46</f>
-        <v>184723.69408583755</v>
-      </c>
-      <c r="H46" s="32">
-        <f>E46*F46</f>
-        <v>184723.69408583755</v>
-      </c>
-      <c r="I46" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="G47" s="32">
+        <f>D47*F47</f>
+        <v>190884.94408583757</v>
+      </c>
+      <c r="H47" s="32">
+        <f>E47*F47</f>
+        <v>190884.94408583757</v>
+      </c>
+      <c r="I47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>mt_dame</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Dame sauteuse (location)</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D47" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A47,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>2.092762499999999</v>
-      </c>
-      <c r="E47" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A47)</f>
-        <v>2.092762499999999</v>
-      </c>
-      <c r="F47" s="32">
+      <c r="D48" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A48,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>2.7176624999999994</v>
+      </c>
+      <c r="E48" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A48)</f>
+        <v>2.7176624999999994</v>
+      </c>
+      <c r="F48" s="32">
         <f>px_mt_dame</f>
         <v>20000.0</v>
       </c>
-      <c r="G47" s="32">
-        <f>D47*F47</f>
-        <v>41855.249999999985</v>
-      </c>
-      <c r="H47" s="32">
-        <f>E47*F47</f>
-        <v>41855.249999999985</v>
-      </c>
-      <c r="I47" s="10" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="G48" s="32">
+        <f>D48*F48</f>
+        <v>54353.249999999985</v>
+      </c>
+      <c r="H48" s="32">
+        <f>E48*F48</f>
+        <v>54353.249999999985</v>
+      </c>
+      <c r="I48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>mt_plaque</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Compacteur à plaque vibrante / rouleau 1 t (location)</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D48" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A48,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D49" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A49,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>2.940225</v>
       </c>
-      <c r="E48" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A48)</f>
+      <c r="E49" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A49)</f>
         <v>2.940225</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F49" s="32">
         <f>px_mt_plaque</f>
         <v>60000.0</v>
       </c>
-      <c r="G48" s="32">
-        <f>D48*F48</f>
+      <c r="G49" s="32">
+        <f>D49*F49</f>
         <v>176413.5</v>
       </c>
-      <c r="H48" s="32">
-        <f>E48*F48</f>
+      <c r="H49" s="32">
+        <f>E49*F49</f>
         <v>176413.5</v>
       </c>
-      <c r="I48" s="10" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>mt_cam</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Camion benne 10 m³</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>voyage</t>
         </is>
       </c>
-      <c r="D49" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A49,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>17.689218750000002</v>
-      </c>
-      <c r="E49" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A49)</f>
-        <v>17.689218750000002</v>
-      </c>
-      <c r="F49" s="32">
+      <c r="D50" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A50,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>18.01696875</v>
+      </c>
+      <c r="E50" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A50)</f>
+        <v>18.01696875</v>
+      </c>
+      <c r="F50" s="32">
         <f>px_mt_cam</f>
         <v>25000.0</v>
       </c>
-      <c r="G49" s="32">
-        <f>D49*F49</f>
-        <v>442230.46875000006</v>
-      </c>
-      <c r="H49" s="32">
-        <f>E49*F49</f>
-        <v>442230.46875000006</v>
-      </c>
-      <c r="I49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="G50" s="32">
+        <f>D50*F50</f>
+        <v>450424.21875</v>
+      </c>
+      <c r="H50" s="32">
+        <f>E50*F50</f>
+        <v>450424.21875</v>
+      </c>
+      <c r="I50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>mt_scie</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Scie à sol (location)</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D50" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A50,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D51" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A51,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>1.3208333333333333</v>
       </c>
-      <c r="E50" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A50)</f>
+      <c r="E51" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A51)</f>
         <v>1.3208333333333333</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F51" s="32">
         <f>px_mt_scie</f>
         <v>30000.0</v>
       </c>
-      <c r="G50" s="32">
-        <f>D50*F50</f>
+      <c r="G51" s="32">
+        <f>D51*F51</f>
         <v>39625.0</v>
       </c>
-      <c r="H50" s="32">
-        <f>E50*F50</f>
+      <c r="H51" s="32">
+        <f>E51*F51</f>
         <v>39625.0</v>
       </c>
-      <c r="I50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>mt_niveau</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Niveau / théodolite (location)</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D51" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A51,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D52" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A52,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>2.0</v>
       </c>
-      <c r="E51" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A51)</f>
+      <c r="E52" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A52)</f>
         <v>2.0</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F52" s="32">
         <f>px_mt_niveau</f>
         <v>15000.0</v>
       </c>
-      <c r="G51" s="32">
-        <f>D51*F51</f>
+      <c r="G52" s="32">
+        <f>D52*F52</f>
         <v>30000.0</v>
       </c>
-      <c r="H51" s="32">
-        <f>E51*F51</f>
+      <c r="H52" s="32">
+        <f>E52*F52</f>
         <v>30000.0</v>
       </c>
-      <c r="I51" s="10" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>mt_branch</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Branchements provisoires eau et électricité</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>ft</t>
         </is>
       </c>
-      <c r="D52" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A52,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D53" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A53,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>1.0</v>
       </c>
-      <c r="E52" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A52)</f>
+      <c r="E53" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A53)</f>
         <v>1.0</v>
       </c>
-      <c r="F52" s="32">
+      <c r="F53" s="32">
         <f>px_mt_branch</f>
         <v>100000.0</v>
       </c>
-      <c r="G52" s="32">
-        <f>D52*F52</f>
+      <c r="G53" s="32">
+        <f>D53*F53</f>
         <v>100000.0</v>
       </c>
-      <c r="H52" s="32">
-        <f>E52*F52</f>
+      <c r="H53" s="32">
+        <f>E53*F53</f>
         <v>100000.0</v>
       </c>
-      <c r="I52" s="10" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>mt_ch</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Poste à souder, meuleuse, levage (charpente)</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D53" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A53,'Sous-détails'!$K$5:$K$407,"NON")</f>
+      <c r="D54" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A54,'Sous-détails'!$K$5:$K$407,"NON")</f>
         <v>3449.6368727932168</v>
       </c>
-      <c r="E53" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A53)</f>
+      <c r="E54" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A54)</f>
         <v>6939.306872793217</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F54" s="32">
         <f>px_mt_ch</f>
         <v>100.0</v>
       </c>
-      <c r="G53" s="32">
-        <f>D53*F53</f>
-        <v>344963.68727932166</v>
-      </c>
-      <c r="H53" s="32">
-        <f>E53*F53</f>
-        <v>693930.6872793217</v>
-      </c>
-      <c r="I53" s="10" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>mt_echaf</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>Échafaudage (location)</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D54" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A54,'Sous-détails'!$K$5:$K$407,"NON")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E54" s="18">
-        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A54)</f>
-        <v>926.24</v>
-      </c>
-      <c r="F54" s="32">
-        <f>px_mt_echaf</f>
-        <v>150.0</v>
-      </c>
       <c r="G54" s="32">
         <f>D54*F54</f>
-        <v>0.0</v>
+        <v>344963.68727932166</v>
       </c>
       <c r="H54" s="32">
         <f>E54*F54</f>
-        <v>138936.0</v>
+        <v>693930.6872793217</v>
       </c>
       <c r="I54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>mt_portail</t>
+          <t>mt_echaf</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Poste à souder, meuleuse (portail)</t>
+          <t>Échafaudage (location)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D55" s="18">
@@ -29489,11 +29528,11 @@
       </c>
       <c r="E55" s="18">
         <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A55)</f>
-        <v>1.0</v>
+        <v>926.24</v>
       </c>
       <c r="F55" s="32">
-        <f>px_mt_portail</f>
-        <v>150000.0</v>
+        <f>px_mt_echaf</f>
+        <v>150.0</v>
       </c>
       <c r="G55" s="32">
         <f>D55*F55</f>
@@ -29501,30 +29540,68 @@
       </c>
       <c r="H55" s="32">
         <f>E55*F55</f>
+        <v>138936.0</v>
+      </c>
+      <c r="I55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>mt_portail</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Poste à souder, meuleuse (portail)</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D56" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A56,'Sous-détails'!$K$5:$K$407,"NON")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E56" s="18">
+        <f>SUMIFS('Sous-détails'!$J$5:$J$407,'Sous-détails'!$D$5:$D$407,A56)</f>
+        <v>1.0</v>
+      </c>
+      <c r="F56" s="32">
+        <f>px_mt_portail</f>
         <v>150000.0</v>
       </c>
-      <c r="I55" s="10" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="23" t="n"/>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="G56" s="32">
+        <f>D56*F56</f>
+        <v>0.0</v>
+      </c>
+      <c r="H56" s="32">
+        <f>E56*F56</f>
+        <v>150000.0</v>
+      </c>
+      <c r="I56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="n"/>
+      <c r="B57" s="24" t="inlineStr">
         <is>
           <t>TOTAL (contrôle = déboursé sec, hors petit outillage)</t>
         </is>
       </c>
-      <c r="C56" s="23" t="n"/>
-      <c r="D56" s="23" t="n"/>
-      <c r="E56" s="23" t="n"/>
-      <c r="F56" s="23" t="n"/>
-      <c r="G56" s="37">
-        <f>SUM(G5:G55)</f>
-        <v>27649258.177081265</v>
-      </c>
-      <c r="H56" s="37">
-        <f>SUM(H5:H55)</f>
-        <v>39759557.5640576</v>
-      </c>
-      <c r="I56" s="23" t="n"/>
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="23" t="n"/>
+      <c r="E57" s="23" t="n"/>
+      <c r="F57" s="23" t="n"/>
+      <c r="G57" s="37">
+        <f>SUM(G5:G56)</f>
+        <v>25418899.13942683</v>
+      </c>
+      <c r="H57" s="37">
+        <f>SUM(H5:H56)</f>
+        <v>37529198.526403174</v>
+      </c>
+      <c r="I57" s="23" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
